--- a/results/result_evaluation_logs/F_URI_Retrieval_Filtering_Gen1v2.xlsx
+++ b/results/result_evaluation_logs/F_URI_Retrieval_Filtering_Gen1v2.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X51"/>
+  <dimension ref="A1:W51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -544,11 +544,6 @@
           <t>Result String</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>Langfuse Trace ID</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -625,11 +620,6 @@
 &lt;http://www.wikidata.org/entity/Q25095540&gt; &lt;http://www.wikidata.org/entity/P112&gt; &lt;http://www.wikidata.org/entity/Q364841&gt; .</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>17fb58fb-2b13-48fd-bb85-bf0091e1f83b</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -703,11 +693,6 @@
           <t>@prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
 wd:Q20992419 wd:P2408 wd:Q120 .
 wd:Q20992419 wd:P361 wd:Q17516 .</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>604c4ed5-eadf-4c3f-bac6-76f67eac093e</t>
         </is>
       </c>
     </row>
@@ -786,11 +771,6 @@
 wd:Q466774 wd:P184 wd:Q370496 .</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>302e8a57-3f25-4638-925c-5011b9a486ba</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -836,10 +816,10 @@
         <v>2</v>
       </c>
       <c r="O5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q5" t="n">
         <v>5</v>
@@ -869,11 +849,6 @@
 wd:Q72697912 wd:P1552 wd:Q4557532 .</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>7331f615-db8b-4284-9f5c-9a9371726dc1</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -946,11 +921,6 @@
         <is>
           <t>@prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
 wd:Q36771 wd:P569 wd:Q29999 .</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>9d53b355-f039-41a0-8371-83934e57fefb</t>
         </is>
       </c>
     </row>
@@ -1028,11 +998,6 @@
 wd:Q506252 wd:P366 wd:Q177 .</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>4082a171-5703-4a53-bc0e-d180ede06515</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1106,11 +1071,6 @@
           <t>@prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
 wd:Q2226643 wd:P138 wd:Q28937 .
 wd:Q2226643 wd:P31 wd:Q65943 .</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>06897e83-91bc-4f4c-bfd5-4309aab3210d</t>
         </is>
       </c>
     </row>
@@ -1188,11 +1148,6 @@
 wd:Q2808 wd:P50 wd:Q2601034 .
 wd:Q2808 wd:Q146 wd:Q2601034 .
 wd:Q2601034 wd:P264 wd:Q3939773 .</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>c156a300-03fd-40f3-8fe6-1dca303d1dbe</t>
         </is>
       </c>
     </row>
@@ -1274,11 +1229,6 @@
 wd:Q924 wd:P421 wd:Q1773949 .</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>ef596be7-8406-4bbe-a1b1-b3fc2500941d</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1354,11 +1304,6 @@
 wd:Q85563 wd:P3373 wd:Q91204 .</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>f38caa6c-c0ec-4541-8b5d-107551e99567</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1374,7 +1319,7 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -1383,7 +1328,7 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1392,7 +1337,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -1413,7 +1358,7 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -1422,7 +1367,7 @@
         <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1488,11 +1433,6 @@
 </t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>6d216be0-5a20-4915-84fd-9e2bb2d52be2</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1568,11 +1508,6 @@
 wd:Q516760 wd:P276 wd:Q1605654 .</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>6dedcbfd-aa6a-4352-ab03-eb508a9f982c</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1618,10 +1553,10 @@
         <v>1</v>
       </c>
       <c r="O14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q14" t="n">
         <v>2</v>
@@ -1648,11 +1583,6 @@
 wd:Q3561541 wd:P206 wd:Q5364109 .</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>cd62a385-2023-4a15-a792-99345a6ddf22</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1727,11 +1657,6 @@
 @prefix dbo: &lt;http://dbpedia.org/ontology/&gt; .</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>fc81397f-f2ad-4713-8dc7-3cac70d920a7</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1806,11 +1731,6 @@
 &lt;http://www.wikidata.org/entity/Q3311362&gt; &lt;http://www.wikidata.org/entity/P131&gt; &lt;http://www.wikidata.org/entity/Q66117&gt; .</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>f350a30f-cd52-497d-981d-9a9819dd113d</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1884,11 +1804,6 @@
           <t>@prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
 wd:Q7044514 wd:P31 wd:Q46046 .
 wd:Q7044514 wd:P175 wd:Q234199 .</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>4dc4d6dd-763e-4f58-a9df-2b7fa768c0c5</t>
         </is>
       </c>
     </row>
@@ -1967,11 +1882,6 @@
 wd:Q607380 wd:P5588 wd:Q782 .</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>88e4cf66-6175-45c0-a188-9213c113852c</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2017,10 +1927,10 @@
         <v>2</v>
       </c>
       <c r="O19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q19" t="n">
         <v>5</v>
@@ -2052,11 +1962,6 @@
 wd:Q5686841 wd:P527 wd:Q794 .</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>5fcd7952-1014-442d-a92f-2fb406d9d902</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2129,11 +2034,6 @@
         <is>
           <t>@prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
 &lt;http://www.wikidata.org/entity/Q20671544&gt; &lt;http://www.wikidata.org/entity/P527&gt; &lt;http://www.wikidata.org/entity/Q27914&gt; .</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>c730f924-6e61-4bcf-aef1-1c47eefcf793</t>
         </is>
       </c>
     </row>
@@ -2214,11 +2114,6 @@
 wd:Q16 wd:P122 wd:Q41614 .</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>0776efda-7926-42df-897f-3c7cd0494531</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2292,11 +2187,6 @@
           <t>@prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
 &lt;http://www.wikidata.org/entity/Q17052475&gt; &lt;http://www.wikidata.org/entity/P361&gt; &lt;http://www.wikidata.org/entity/Q11348&gt; .
 &lt;http://www.wikidata.org/entity/Q17052475&gt; &lt;http://www.wikidata.org/entity/P361&gt; &lt;http://www.wikidata.org/entity/Q395&gt; .</t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>ae9fbdea-9dca-43cb-803f-7f2bf8006e2d</t>
         </is>
       </c>
     </row>
@@ -2375,11 +2265,6 @@
 wd:Q18036690 wd:P1479 wd:Q12174 .</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>0398e5b3-b9e5-4a7a-96c9-141e7b27c4f2</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2453,11 +2338,6 @@
           <t>@prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
 &lt;http://www.wikidata.org/entity/Q188197&gt; &lt;http://www.wikidata.org/entity/P1346&gt; &lt;http://www.wikidata.org/entity/Q1856183&gt; .
 &lt;http://www.wikidata.org/entity/Q188197&gt; &lt;http://www.wikidata.org/entity/P1346&gt; &lt;http://www.wikidata.org/entity/Q674962&gt; .</t>
-        </is>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>3c83dd7e-2ed9-4074-b6c7-0857f5404b57</t>
         </is>
       </c>
     </row>
@@ -2537,11 +2417,6 @@
 wd:Q5554167 wd:P750 wd:Q520445 .</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>253d6c1e-83c3-42cd-a2ab-b47629c72a1e</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -2557,7 +2432,7 @@
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -2566,7 +2441,7 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -2575,7 +2450,7 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -2596,7 +2471,7 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -2605,7 +2480,7 @@
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -2671,11 +2546,6 @@
 </t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>7bceeec5-f1c1-4fdf-ac0d-ee17d08826ff</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2749,11 +2619,6 @@
           <t>@prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
 wd:Q2094579 wd:P287 wd:Q5546527 .
 wd:Q5546527 wd:P138 wd:Q8229 .</t>
-        </is>
-      </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>3a9bc1bb-8c55-4230-b199-6e42fc0afcae</t>
         </is>
       </c>
     </row>
@@ -2830,11 +2695,6 @@
 &lt;http://www.wikidata.org/entity/Q22082365&gt; &lt;http://www.wikidata.org/entity/P527&gt; &lt;http://www.wikidata.org/entity/Q3957&gt; .
 &lt;http://www.wikidata.org/entity/Q965&gt; &lt;http://www.wikidata.org/entity/P463&gt; &lt;http://www.wikidata.org/entity/Q47543&gt; .
 &lt;http://www.wikidata.org/entity/Q22082365&gt; &lt;http://www.wikidata.org/entity/P131&gt; &lt;http://www.wikidata.org/entity/Q965&gt; .</t>
-        </is>
-      </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>e386af8f-51de-4cae-8056-b782aa8e7336</t>
         </is>
       </c>
     </row>
@@ -2915,11 +2775,6 @@
 wd:Q6762533 wd:P131 wd:Q408 .</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>037902f5-a787-4bb3-8dfe-43f44716de7e</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2935,7 +2790,7 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -2944,7 +2799,7 @@
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -2953,7 +2808,7 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -2974,7 +2829,7 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -2983,7 +2838,7 @@
         <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
         <v>0</v>
@@ -3049,11 +2904,6 @@
 </t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>a8b60247-6d85-45c0-90f6-a7f0ebb91266</t>
-        </is>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3133,11 +2983,6 @@
 wd:Q304801 wd:P131 wd:Q1384 .</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>470157f2-f9af-476f-9e6c-3c63f0654af2</t>
-        </is>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3212,11 +3057,6 @@
 wd:Q64876878 wd:P674 wd:Q65090308 .
 wd:Q65090308 wd:P674 wd:Q64876878 .
 wd:Q64876878 wd:P725 wd:Q262170 .</t>
-        </is>
-      </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>42d1663b-8769-4234-80e3-40b3c2b495d7</t>
         </is>
       </c>
     </row>
@@ -3297,11 +3137,6 @@
 &lt;http://www.wikidata.org/entity/Q1240173&gt; &lt;http://www.wikidata.org/entity/P149&gt; &lt;http://www.wikidata.org/entity/Q2722661&gt; .</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>18db2f8a-eabb-44ff-9b59-5dc9a53bb600</t>
-        </is>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3378,11 +3213,6 @@
 wd:Q822946 wd:P361 wd:Q130232 .</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>6d05873b-8e49-4a6f-8258-af0a79c2b119</t>
-        </is>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3459,11 +3289,6 @@
 wd:Q5072388 wd:P1441 wd:Q41792848 .</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>2f0a1af8-d74f-4de7-8a3f-8bbf6094f68a</t>
-        </is>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -3538,11 +3363,6 @@
 wd:Q1490434 wd:P361 wd:Q41298 .</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>2533fc3e-67d0-4af7-966f-22d06a93b156</t>
-        </is>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -3588,10 +3408,10 @@
         <v>1</v>
       </c>
       <c r="O37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q37" t="n">
         <v>3</v>
@@ -3619,11 +3439,6 @@
 wd:Q2616869 wd:P361 wd:Q19652 .</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>090b37b6-c122-4e1e-8a67-cfb42b64b8c1</t>
-        </is>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -3669,10 +3484,10 @@
         <v>2</v>
       </c>
       <c r="O38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q38" t="n">
         <v>4</v>
@@ -3702,11 +3517,6 @@
 wd:Q1084560 wd:P361 wd:Q1247390 .</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>e56275e5-761c-4777-8478-318f1415f5d1</t>
-        </is>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -3780,11 +3590,6 @@
           <t>@prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
 wd:Q907827 wd:P131 wd:Q183 .
 wd:Q907827 wd:P1546 wd:Q877781 .</t>
-        </is>
-      </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>cd5df52a-5cb4-4704-9a40-596ed8ce4476</t>
         </is>
       </c>
     </row>
@@ -3863,11 +3668,6 @@
 wd:Q1064344 wd:P527 wd:Q1064344 .</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>00b98626-1acb-476f-96ef-3197e6d12cbd</t>
-        </is>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -3943,11 +3743,6 @@
 &lt;http://www.wikidata.org/entity/Q47554&gt; &lt;http://www.wikidata.org/entity/P706&gt; &lt;http://www.wikidata.org/entity/Q1261531&gt; .</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>7f30e457-9696-4921-a3ef-a2bb5fb5911e</t>
-        </is>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -3987,7 +3782,7 @@
         <v>3</v>
       </c>
       <c r="M42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N42" t="n">
         <v>4</v>
@@ -4028,11 +3823,6 @@
 wd:Q16568 wd:P131 wd:Q11696 .</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>29996801-7fab-422c-a4cc-2353b4680cf7</t>
-        </is>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4106,11 +3896,6 @@
           <t>@prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
 wd:Q87412161 wd:P3373 wd:Q95994024 .
 wd:Q87412161 wd:P31 wd:Q5 .</t>
-        </is>
-      </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>8dc2a4e7-c420-4768-b259-d648c3e24ede</t>
         </is>
       </c>
     </row>
@@ -4187,11 +3972,6 @@
 &lt;http://www.wikidata.org/entity/Q29644512&gt; &lt;http://www.wikidata.org/entity/P1454&gt; &lt;http://www.wikidata.org/entity/Q152074&gt; .
 &lt;http://www.wikidata.org/entity/Q152074&gt; &lt;http://www.wikidata.org/entity/P2348&gt; "2017" .
 &lt;http://www.wikidata.org/entity/Q29644512&gt; &lt;http://www.wikidata.org/entity/P136&gt; &lt;http://www.wikidata.org/entity/Q1358919&gt; .</t>
-        </is>
-      </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>d48f3351-f126-4d3e-9981-c7b0df5524d6</t>
         </is>
       </c>
     </row>
@@ -4273,11 +4053,6 @@
 wd:Q5288565 wd:P528 wd:Q7368 .</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>d5e8fdd2-75ff-4930-8f22-dad51b155047</t>
-        </is>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -4354,11 +4129,6 @@
 wd:Q92560 wd:P449 wd:Q734663 .</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>5aab88a9-77dc-4ae8-b2c2-fbe156ae7508</t>
-        </is>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -4432,11 +4202,6 @@
           <t>@prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
 &lt;http://www.wikidata.org/entity/Q18036732&gt; &lt;http://www.wikidata.org/entity/P276&gt; &lt;http://www.wikidata.org/entity/Q753805&gt; .
 &lt;http://www.wikidata.org/entity/Q18036732&gt; &lt;http://www.wikidata.org/entity/P361&gt; &lt;http://www.wikidata.org/entity/Q7187&gt; .</t>
-        </is>
-      </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>fb111a16-7f24-4bc1-88c5-daf6029fe8b2</t>
         </is>
       </c>
     </row>
@@ -4513,11 +4278,6 @@
 &lt;http://www.wikidata.org/entity/Q977911&gt; &lt;http://www.wikidata.org/entity/P131&gt; &lt;http://www.wikidata.org/entity/Q112686&gt; .
 &lt;http://www.wikidata.org/entity/Q977911&gt; &lt;http://www.wikidata.org/entity/P47&gt; &lt;http://www.wikidata.org/entity/Q979352&gt; .
 &lt;http://www.wikidata.org/entity/Q979352&gt; &lt;http://www.wikidata.org/entity/P131&gt; &lt;http://www.wikidata.org/entity/Q112686&gt; .</t>
-        </is>
-      </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>c32d7522-90b1-413a-963a-62c9ebe969c0</t>
         </is>
       </c>
     </row>
@@ -4598,11 +4358,6 @@
 &lt;http://www.wikidata.org/entity/Q4546576&gt; &lt;http://www.wikidata.org/entity/P155&gt; &lt;http://www.wikidata.org/entity/Q311849&gt; .</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>ed081df6-2ef6-4e11-a1bf-58f731d1191d</t>
-        </is>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -4648,10 +4403,10 @@
         <v>2</v>
       </c>
       <c r="O50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q50" t="n">
         <v>3</v>
@@ -4679,11 +4434,6 @@
 wd:Q2822458 wd:P361 wd:Q1140115 .</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>ca484a4a-c7b4-4578-84b3-4a72f9a89636</t>
-        </is>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -4756,11 +4506,6 @@
         <is>
           <t>@prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
 &lt;http://www.wikidata.org/entity/Q2362697&gt; &lt;http://www.wikidata.org/entity/P556&gt; &lt;http://www.wikidata.org/entity/Q503601&gt; .</t>
-        </is>
-      </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>0970c7f6-9350-44c9-9c66-d0384f2dfcc2</t>
         </is>
       </c>
     </row>

--- a/results/result_evaluation_logs/F_URI_Retrieval_Filtering_Gen1v2.xlsx
+++ b/results/result_evaluation_logs/F_URI_Retrieval_Filtering_Gen1v2.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W51"/>
+  <dimension ref="A1:X51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -544,25 +544,30 @@
           <t>Result String</t>
         </is>
       </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Langfuse Trace ID</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
         <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
@@ -574,28 +579,28 @@
         <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K2" t="n">
         <v>2</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R2" t="n">
         <v>2</v>
@@ -615,9 +620,13 @@
       <c r="W2" t="inlineStr">
         <is>
           <t>@prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
-&lt;http://www.wikidata.org/entity/Q25095540&gt; &lt;http://www.wikidata.org/entity/P527&gt; &lt;http://www.wikidata.org/entity/Q25095540&gt; .
-&lt;http://www.wikidata.org/entity/Q25095540&gt; &lt;http://www.wikidata.org/entity/P1433&gt; &lt;http://www.wikidata.org/entity/Q1516254&gt; .
-&lt;http://www.wikidata.org/entity/Q25095540&gt; &lt;http://www.wikidata.org/entity/P112&gt; &lt;http://www.wikidata.org/entity/Q364841&gt; .</t>
+wd:Q25095540 wd:P1433 wd:Q1516254 .
+wd:Q25095540 wd:P175 wd:Q364841 .</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>a42dd3c4-4f85-4004-9906-f7f53ded9c77</t>
         </is>
       </c>
     </row>
@@ -638,19 +647,19 @@
         <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
         <v>2</v>
@@ -671,710 +680,26 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>2</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
         <v>3</v>
       </c>
       <c r="V3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>@prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
-wd:Q20992419 wd:P2408 wd:Q120 .
-wd:Q20992419 wd:P361 wd:Q17516 .</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E4" t="n">
-        <v>5</v>
-      </c>
-      <c r="F4" t="n">
-        <v>3</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" t="n">
-        <v>3</v>
-      </c>
-      <c r="K4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L4" t="n">
-        <v>2</v>
-      </c>
-      <c r="M4" t="n">
-        <v>3</v>
-      </c>
-      <c r="N4" t="n">
-        <v>3</v>
-      </c>
-      <c r="O4" t="n">
-        <v>3</v>
-      </c>
-      <c r="P4" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>3</v>
-      </c>
-      <c r="R4" t="n">
-        <v>5</v>
-      </c>
-      <c r="S4" t="n">
-        <v>3</v>
-      </c>
-      <c r="T4" t="n">
-        <v>4</v>
-      </c>
-      <c r="U4" t="n">
-        <v>6</v>
-      </c>
-      <c r="V4" t="n">
-        <v>4</v>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>@prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
-wd:Q466774 wd:P361 wd:Q395 .
-wd:Q466774 wd:P108 wd:Q273626 .
-wd:Q466774 wd:P184 wd:Q370496 .</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" t="n">
-        <v>6</v>
-      </c>
-      <c r="F5" t="n">
-        <v>5</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" t="n">
-        <v>5</v>
-      </c>
-      <c r="K5" t="n">
-        <v>6</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1</v>
-      </c>
-      <c r="M5" t="n">
-        <v>2</v>
-      </c>
-      <c r="N5" t="n">
-        <v>2</v>
-      </c>
-      <c r="O5" t="n">
-        <v>2</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>5</v>
-      </c>
-      <c r="R5" t="n">
-        <v>6</v>
-      </c>
-      <c r="S5" t="n">
-        <v>5</v>
-      </c>
-      <c r="T5" t="n">
-        <v>6</v>
-      </c>
-      <c r="U5" t="n">
-        <v>7</v>
-      </c>
-      <c r="V5" t="n">
-        <v>6</v>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>@prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
-wd:Q72697912 wd:P527 wd:Q11424 .
-wd:Q72697912 wd:P750 wd:Q723685 .
-wd:Q72697912 wd:P921 wd:Q1993848 .
-wd:Q72697912 wd:P2408 wd:Q81725 .
-wd:Q72697912 wd:P1552 wd:Q4557532 .</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2</v>
-      </c>
-      <c r="U6" t="n">
-        <v>2</v>
-      </c>
-      <c r="V6" t="n">
-        <v>2</v>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>@prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
-wd:Q36771 wd:P569 wd:Q29999 .</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="n">
-        <v>3</v>
-      </c>
-      <c r="F7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J7" t="n">
-        <v>2</v>
-      </c>
-      <c r="K7" t="n">
-        <v>3</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2</v>
-      </c>
-      <c r="R7" t="n">
-        <v>3</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3</v>
-      </c>
-      <c r="U7" t="n">
-        <v>4</v>
-      </c>
-      <c r="V7" t="n">
-        <v>3</v>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>@prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
-wd:Q506252 wd:P527 wd:Q192786 .
-wd:Q506252 wd:P366 wd:Q177 .</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>6</v>
-      </c>
-      <c r="B8" t="n">
-        <v>2</v>
-      </c>
-      <c r="C8" t="n">
-        <v>2</v>
-      </c>
-      <c r="D8" t="n">
-        <v>2</v>
-      </c>
-      <c r="E8" t="n">
-        <v>2</v>
-      </c>
-      <c r="F8" t="n">
-        <v>2</v>
-      </c>
-      <c r="G8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" t="n">
-        <v>2</v>
-      </c>
-      <c r="K8" t="n">
-        <v>2</v>
-      </c>
-      <c r="L8" t="n">
-        <v>2</v>
-      </c>
-      <c r="M8" t="n">
-        <v>2</v>
-      </c>
-      <c r="N8" t="n">
-        <v>2</v>
-      </c>
-      <c r="O8" t="n">
-        <v>2</v>
-      </c>
-      <c r="P8" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2</v>
-      </c>
-      <c r="R8" t="n">
-        <v>2</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3</v>
-      </c>
-      <c r="U8" t="n">
-        <v>3</v>
-      </c>
-      <c r="V8" t="n">
-        <v>3</v>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>@prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
-wd:Q2226643 wd:P138 wd:Q28937 .
-wd:Q2226643 wd:P31 wd:Q65943 .</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>7</v>
-      </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" t="n">
-        <v>6</v>
-      </c>
-      <c r="F9" t="n">
-        <v>4</v>
-      </c>
-      <c r="G9" t="n">
-        <v>2</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J9" t="n">
-        <v>4</v>
-      </c>
-      <c r="K9" t="n">
-        <v>6</v>
-      </c>
-      <c r="L9" t="n">
-        <v>2</v>
-      </c>
-      <c r="M9" t="n">
-        <v>2</v>
-      </c>
-      <c r="N9" t="n">
-        <v>2</v>
-      </c>
-      <c r="O9" t="n">
-        <v>2</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>3</v>
-      </c>
-      <c r="R9" t="n">
-        <v>6</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T9" t="n">
-        <v>4</v>
-      </c>
-      <c r="U9" t="n">
-        <v>7</v>
-      </c>
-      <c r="V9" t="n">
-        <v>3</v>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>@prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
-wd:Q2601034 wd:P175 wd:Q6781136 .
-wd:Q2808 wd:P50 wd:Q2601034 .
-wd:Q2808 wd:Q146 wd:Q2601034 .
-wd:Q2601034 wd:P264 wd:Q3939773 .</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>8</v>
-      </c>
-      <c r="B10" t="n">
-        <v>3</v>
-      </c>
-      <c r="C10" t="n">
-        <v>3</v>
-      </c>
-      <c r="D10" t="n">
-        <v>3</v>
-      </c>
-      <c r="E10" t="n">
-        <v>7</v>
-      </c>
-      <c r="F10" t="n">
-        <v>6</v>
-      </c>
-      <c r="G10" t="n">
-        <v>3</v>
-      </c>
-      <c r="H10" t="n">
-        <v>3</v>
-      </c>
-      <c r="I10" t="n">
-        <v>2</v>
-      </c>
-      <c r="J10" t="n">
-        <v>4</v>
-      </c>
-      <c r="K10" t="n">
-        <v>7</v>
-      </c>
-      <c r="L10" t="n">
-        <v>4</v>
-      </c>
-      <c r="M10" t="n">
-        <v>5</v>
-      </c>
-      <c r="N10" t="n">
-        <v>5</v>
-      </c>
-      <c r="O10" t="n">
-        <v>4</v>
-      </c>
-      <c r="P10" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>4</v>
-      </c>
-      <c r="R10" t="n">
-        <v>7</v>
-      </c>
-      <c r="S10" t="n">
-        <v>4</v>
-      </c>
-      <c r="T10" t="n">
-        <v>7</v>
-      </c>
-      <c r="U10" t="n">
-        <v>8</v>
-      </c>
-      <c r="V10" t="n">
-        <v>7</v>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>@prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
-wd:Q6782514 wd:P131 wd:Q1364658 .
-wd:Q6782514 wd:P421 wd:Q1773949 .
-wd:Q924 wd:P1906 wd:Q7241291 .
-wd:Q924 wd:P37 wd:Q7838 .
-wd:Q423 wd:P421 wd:Q1773949 .
-wd:Q924 wd:P421 wd:Q1773949 .</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>9</v>
-      </c>
-      <c r="B11" t="n">
-        <v>2</v>
-      </c>
-      <c r="C11" t="n">
-        <v>2</v>
-      </c>
-      <c r="D11" t="n">
-        <v>2</v>
-      </c>
-      <c r="E11" t="n">
-        <v>5</v>
-      </c>
-      <c r="F11" t="n">
-        <v>2</v>
-      </c>
-      <c r="G11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" t="n">
-        <v>2</v>
-      </c>
-      <c r="I11" t="n">
-        <v>1</v>
-      </c>
-      <c r="J11" t="n">
-        <v>2</v>
-      </c>
-      <c r="K11" t="n">
-        <v>5</v>
-      </c>
-      <c r="L11" t="n">
-        <v>2</v>
-      </c>
-      <c r="M11" t="n">
-        <v>2</v>
-      </c>
-      <c r="N11" t="n">
-        <v>2</v>
-      </c>
-      <c r="O11" t="n">
-        <v>2</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2</v>
-      </c>
-      <c r="R11" t="n">
-        <v>5</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3</v>
-      </c>
-      <c r="U11" t="n">
-        <v>6</v>
-      </c>
-      <c r="V11" t="n">
-        <v>3</v>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>@prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
-wd:Q85563 wd:P26 wd:Q58284 .
-wd:Q85563 wd:P3373 wd:Q91204 .</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>10</v>
-      </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Error: Error code: 400 - {'object': 'error', 'message': "This model's maximum context length is 8192 tokens. However, you requested 8200 tokens in the messages, Please reduce the length of the messages.", 'type': 'BadRequestError', 'param': None, 'code': 400}
+          <t xml:space="preserve">Error: Error code: 400 - {'object': 'error', 'message': "This model's maximum context length is 8192 tokens. However, you requested 8203 tokens in the messages, Please reduce the length of the messages.", 'type': 'BadRequestError', 'param': None, 'code': 400}
 Traceback:
 Traceback (most recent call last):
   File "/home/mlautenb/CIExMAS/./results/F_URI_Retrieval_Filtering/Gen1v2/slurm/agent_system.py", line 78, in &lt;module&gt;
@@ -1428,1066 +753,584 @@
            ^^^^^^^^^^^^^^
   File "/home/mlautenb/miniconda3/envs/CIExMAS/lib/python3.11/site-packages/openai/_base_client.py", line 1023, in _request
     raise self._make_status_error_from_response(err.response) from None
-openai.BadRequestError: Error code: 400 - {'object': 'error', 'message': "This model's maximum context length is 8192 tokens. However, you requested 8200 tokens in the messages, Please reduce the length of the messages.", 'type': 'BadRequestError', 'param': None, 'code': 400}
-During task with name 'planner' and id '89f442df-30bc-ad4e-0a46-d284619f1572'
+openai.BadRequestError: Error code: 400 - {'object': 'error', 'message': "This model's maximum context length is 8192 tokens. However, you requested 8203 tokens in the messages, Please reduce the length of the messages.", 'type': 'BadRequestError', 'param': None, 'code': 400}
+During task with name 'planner' and id 'aa064052-d3c3-cadf-58f9-394040c86272'
 </t>
         </is>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>11</v>
-      </c>
-      <c r="B13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" t="n">
-        <v>2</v>
-      </c>
-      <c r="F13" t="n">
-        <v>2</v>
-      </c>
-      <c r="G13" t="n">
-        <v>2</v>
-      </c>
-      <c r="H13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I13" t="n">
-        <v>1</v>
-      </c>
-      <c r="J13" t="n">
-        <v>2</v>
-      </c>
-      <c r="K13" t="n">
-        <v>2</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1</v>
-      </c>
-      <c r="N13" t="n">
-        <v>1</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1</v>
-      </c>
-      <c r="P13" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>2</v>
-      </c>
-      <c r="R13" t="n">
-        <v>2</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1</v>
-      </c>
-      <c r="T13" t="n">
-        <v>3</v>
-      </c>
-      <c r="U13" t="n">
-        <v>3</v>
-      </c>
-      <c r="V13" t="n">
-        <v>3</v>
-      </c>
-      <c r="W13" t="inlineStr">
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>9ce78bf5-5dab-4949-aa4b-dbf5929b0d7e</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F4" t="n">
+        <v>4</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J4" t="n">
+        <v>4</v>
+      </c>
+      <c r="K4" t="n">
+        <v>5</v>
+      </c>
+      <c r="L4" t="n">
+        <v>3</v>
+      </c>
+      <c r="M4" t="n">
+        <v>3</v>
+      </c>
+      <c r="N4" t="n">
+        <v>3</v>
+      </c>
+      <c r="O4" t="n">
+        <v>3</v>
+      </c>
+      <c r="P4" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>4</v>
+      </c>
+      <c r="R4" t="n">
+        <v>5</v>
+      </c>
+      <c r="S4" t="n">
+        <v>4</v>
+      </c>
+      <c r="T4" t="n">
+        <v>5</v>
+      </c>
+      <c r="U4" t="n">
+        <v>6</v>
+      </c>
+      <c r="V4" t="n">
+        <v>5</v>
+      </c>
+      <c r="W4" t="inlineStr">
         <is>
           <t>@prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
-wd:Q271108 wd:P134 wd:Q516760 .
-wd:Q516760 wd:P276 wd:Q1605654 .</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>12</v>
-      </c>
-      <c r="B14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E14" t="n">
-        <v>3</v>
-      </c>
-      <c r="F14" t="n">
-        <v>2</v>
-      </c>
-      <c r="G14" t="n">
-        <v>2</v>
-      </c>
-      <c r="H14" t="n">
-        <v>2</v>
-      </c>
-      <c r="I14" t="n">
-        <v>2</v>
-      </c>
-      <c r="J14" t="n">
-        <v>2</v>
-      </c>
-      <c r="K14" t="n">
-        <v>3</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1</v>
-      </c>
-      <c r="N14" t="n">
-        <v>1</v>
-      </c>
-      <c r="O14" t="n">
-        <v>2</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>2</v>
-      </c>
-      <c r="R14" t="n">
-        <v>3</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3</v>
-      </c>
-      <c r="U14" t="n">
-        <v>3</v>
-      </c>
-      <c r="V14" t="n">
-        <v>3</v>
-      </c>
-      <c r="W14" t="inlineStr">
+wd:Q466774 wd:P184 wd:Q370496 .
+wd:Q466774 wd:P108 wd:Q273626 .
+wd:Q142 wd:P194 wd:Q632552 .
+wd:Q466774 wd:P27 wd:Q142 .</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>55753659-b7f6-4fc1-945d-469980f86d4c</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>6</v>
+      </c>
+      <c r="F5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>4</v>
+      </c>
+      <c r="K5" t="n">
+        <v>6</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>4</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6</v>
+      </c>
+      <c r="S5" t="n">
+        <v>4</v>
+      </c>
+      <c r="T5" t="n">
+        <v>6</v>
+      </c>
+      <c r="U5" t="n">
+        <v>7</v>
+      </c>
+      <c r="V5" t="n">
+        <v>6</v>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>@prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
-wd:Q7992209 wd:P4661 wd:Q3561541 .
-wd:Q3561541 wd:P206 wd:Q5364109 .</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>13</v>
-      </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>4</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>1</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>4</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>4</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="n">
-        <v>5</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>@prefix dbp: &lt;http://dbpedia.org/resource/&gt; .
-@prefix dbo: &lt;http://dbpedia.org/ontology/&gt; .</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>14</v>
-      </c>
-      <c r="B16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" t="n">
-        <v>1</v>
-      </c>
-      <c r="G16" t="n">
-        <v>1</v>
-      </c>
-      <c r="H16" t="n">
-        <v>1</v>
-      </c>
-      <c r="I16" t="n">
-        <v>1</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1</v>
-      </c>
-      <c r="N16" t="n">
-        <v>1</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1</v>
-      </c>
-      <c r="P16" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2</v>
-      </c>
-      <c r="U16" t="n">
-        <v>2</v>
-      </c>
-      <c r="V16" t="n">
-        <v>2</v>
-      </c>
-      <c r="W16" t="inlineStr">
+wd:Q81725 wd:P131 wd:Q258 .
+wd:Q72697912 wd:P179 wd:Q1993848 .
+wd:Q72697912 wd:P166 wd:Q4557532 .
+wd:Q72697912 wd:P750 wd:Q723685 .</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>77745a6f-1b09-4042-863c-3eab9b0d378d</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2</v>
+      </c>
+      <c r="V6" t="n">
+        <v>2</v>
+      </c>
+      <c r="W6" t="inlineStr">
         <is>
           <t>@prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
-&lt;http://www.wikidata.org/entity/Q3311362&gt; &lt;http://www.wikidata.org/entity/P131&gt; &lt;http://www.wikidata.org/entity/Q66117&gt; .</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>15</v>
-      </c>
-      <c r="B17" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" t="n">
-        <v>1</v>
-      </c>
-      <c r="D17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E17" t="n">
-        <v>3</v>
-      </c>
-      <c r="F17" t="n">
-        <v>2</v>
-      </c>
-      <c r="G17" t="n">
-        <v>1</v>
-      </c>
-      <c r="H17" t="n">
-        <v>1</v>
-      </c>
-      <c r="I17" t="n">
-        <v>1</v>
-      </c>
-      <c r="J17" t="n">
-        <v>2</v>
-      </c>
-      <c r="K17" t="n">
-        <v>3</v>
-      </c>
-      <c r="L17" t="n">
-        <v>2</v>
-      </c>
-      <c r="M17" t="n">
-        <v>2</v>
-      </c>
-      <c r="N17" t="n">
-        <v>2</v>
-      </c>
-      <c r="O17" t="n">
-        <v>2</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2</v>
-      </c>
-      <c r="R17" t="n">
-        <v>3</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3</v>
-      </c>
-      <c r="U17" t="n">
-        <v>4</v>
-      </c>
-      <c r="V17" t="n">
-        <v>3</v>
-      </c>
-      <c r="W17" t="inlineStr">
+wd:Q36771 wd:P27 wd:Q29999 .</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>e1d88783-62de-4633-8b25-5ea46c321c5b</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" t="n">
+        <v>4</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3</v>
+      </c>
+      <c r="R7" t="n">
+        <v>3</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3</v>
+      </c>
+      <c r="T7" t="n">
+        <v>4</v>
+      </c>
+      <c r="U7" t="n">
+        <v>4</v>
+      </c>
+      <c r="V7" t="n">
+        <v>4</v>
+      </c>
+      <c r="W7" t="inlineStr">
         <is>
           <t>@prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
-wd:Q7044514 wd:P31 wd:Q46046 .
-wd:Q7044514 wd:P175 wd:Q234199 .</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>16</v>
-      </c>
-      <c r="B18" t="n">
-        <v>2</v>
-      </c>
-      <c r="C18" t="n">
-        <v>2</v>
-      </c>
-      <c r="D18" t="n">
-        <v>2</v>
-      </c>
-      <c r="E18" t="n">
-        <v>3</v>
-      </c>
-      <c r="F18" t="n">
-        <v>3</v>
-      </c>
-      <c r="G18" t="n">
-        <v>1</v>
-      </c>
-      <c r="H18" t="n">
-        <v>1</v>
-      </c>
-      <c r="I18" t="n">
-        <v>1</v>
-      </c>
-      <c r="J18" t="n">
-        <v>3</v>
-      </c>
-      <c r="K18" t="n">
-        <v>3</v>
-      </c>
-      <c r="L18" t="n">
-        <v>2</v>
-      </c>
-      <c r="M18" t="n">
-        <v>2</v>
-      </c>
-      <c r="N18" t="n">
-        <v>2</v>
-      </c>
-      <c r="O18" t="n">
-        <v>2</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>3</v>
-      </c>
-      <c r="R18" t="n">
-        <v>3</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3</v>
-      </c>
-      <c r="T18" t="n">
-        <v>4</v>
-      </c>
-      <c r="U18" t="n">
-        <v>4</v>
-      </c>
-      <c r="V18" t="n">
-        <v>4</v>
-      </c>
-      <c r="W18" t="inlineStr">
+wd:Q506252 wd:P361 wd:Q279014 .
+wd:Q506252 wd:P366 wd:Q192786 .
+wd:Q506252 wd:P366 wd:Q177 .
+wd:Q192786 wd:P1012 wd:Q177 .</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>aa460ec0-a66f-4d00-9a03-1287aba3e76a</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>3</v>
+      </c>
+      <c r="V8" t="n">
+        <v>3</v>
+      </c>
+      <c r="W8" t="inlineStr">
         <is>
           <t>@prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
-wd:Q607380 wd:P183 wd:Q664 .
-wd:Q607380 wd:P186 wd:Q6933370 .
-wd:Q607380 wd:P5588 wd:Q782 .</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>17</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>4</v>
-      </c>
-      <c r="F19" t="n">
+&lt;http://www.wikidata.org/entity/Q2226643&gt; &lt;http://www.wikidata.org/entity/P31&gt; &lt;http://www.wikidata.org/entity/Q65943&gt; .
+&lt;http://www.wikidata.org/entity/Q2226643&gt; &lt;http://www.wikidata.org/entity/P138&gt; &lt;http://www.wikidata.org/entity/Q28937&gt; .</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>44150d32-5891-4b4a-b699-f40f5eacfbb8</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
         <v>7</v>
       </c>
-      <c r="G19" t="n">
-        <v>4</v>
-      </c>
-      <c r="H19" t="n">
-        <v>2</v>
-      </c>
-      <c r="I19" t="n">
-        <v>2</v>
-      </c>
-      <c r="J19" t="n">
-        <v>3</v>
-      </c>
-      <c r="K19" t="n">
-        <v>3</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1</v>
-      </c>
-      <c r="M19" t="n">
-        <v>2</v>
-      </c>
-      <c r="N19" t="n">
-        <v>2</v>
-      </c>
-      <c r="O19" t="n">
-        <v>3</v>
-      </c>
-      <c r="P19" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>5</v>
-      </c>
-      <c r="R19" t="n">
-        <v>4</v>
-      </c>
-      <c r="S19" t="n">
-        <v>4</v>
-      </c>
-      <c r="T19" t="n">
-        <v>5</v>
-      </c>
-      <c r="U19" t="n">
-        <v>5</v>
-      </c>
-      <c r="V19" t="n">
-        <v>5</v>
-      </c>
-      <c r="W19" t="inlineStr">
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>6</v>
+      </c>
+      <c r="F9" t="n">
+        <v>4</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>4</v>
+      </c>
+      <c r="K9" t="n">
+        <v>6</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>4</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6</v>
+      </c>
+      <c r="S9" t="n">
+        <v>4</v>
+      </c>
+      <c r="T9" t="n">
+        <v>5</v>
+      </c>
+      <c r="U9" t="n">
+        <v>7</v>
+      </c>
+      <c r="V9" t="n">
+        <v>5</v>
+      </c>
+      <c r="W9" t="inlineStr">
         <is>
           <t>@prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
-wd:Q5686841 wd:P150 wd:Q308864 .
-wd:Q308864 wd:P131 wd:Q5686841 .
-wd:Q5686841 wd:P150 wd:Q928828 .
-wd:Q1282219 wd:P131 wd:Q5686841 .
-wd:Q928828 wd:P131 wd:Q5686841 .
-wd:Q5686841 wd:P150 wd:Q1282219 .
-wd:Q5686841 wd:P527 wd:Q794 .</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>18</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>1</v>
-      </c>
-      <c r="F20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G20" t="n">
-        <v>1</v>
-      </c>
-      <c r="H20" t="n">
-        <v>1</v>
-      </c>
-      <c r="I20" t="n">
-        <v>1</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1</v>
-      </c>
-      <c r="K20" t="n">
-        <v>1</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1</v>
-      </c>
-      <c r="S20" t="n">
-        <v>1</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2</v>
-      </c>
-      <c r="U20" t="n">
-        <v>2</v>
-      </c>
-      <c r="V20" t="n">
-        <v>2</v>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>@prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
-&lt;http://www.wikidata.org/entity/Q20671544&gt; &lt;http://www.wikidata.org/entity/P527&gt; &lt;http://www.wikidata.org/entity/Q27914&gt; .</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>19</v>
-      </c>
-      <c r="B21" t="n">
-        <v>4</v>
-      </c>
-      <c r="C21" t="n">
-        <v>4</v>
-      </c>
-      <c r="D21" t="n">
-        <v>4</v>
-      </c>
-      <c r="E21" t="n">
+@prefix wdt: &lt;http://www.wikidata.org/prop/direct/&gt; .
+wd:Q2601034 wdt:P162 wd:Q2338060 .
+wd:Q2601034 wdt:P750 wd:Q3939773 .
+wd:Q2601034 wdt:P175 wd:Q2808 .
+wd:Q2808 wdt:P674 wd:Q11399 .</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>7c172ab8-ae6c-4619-a382-c6b14a428eff</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
         <v>7</v>
       </c>
-      <c r="F21" t="n">
-        <v>5</v>
-      </c>
-      <c r="G21" t="n">
-        <v>2</v>
-      </c>
-      <c r="H21" t="n">
-        <v>2</v>
-      </c>
-      <c r="I21" t="n">
-        <v>2</v>
-      </c>
-      <c r="J21" t="n">
-        <v>5</v>
-      </c>
-      <c r="K21" t="n">
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>3</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
         <v>7</v>
       </c>
-      <c r="L21" t="n">
-        <v>4</v>
-      </c>
-      <c r="M21" t="n">
-        <v>4</v>
-      </c>
-      <c r="N21" t="n">
-        <v>4</v>
-      </c>
-      <c r="O21" t="n">
-        <v>4</v>
-      </c>
-      <c r="P21" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>5</v>
-      </c>
-      <c r="R21" t="n">
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
         <v>7</v>
       </c>
-      <c r="S21" t="n">
-        <v>5</v>
-      </c>
-      <c r="T21" t="n">
-        <v>6</v>
-      </c>
-      <c r="U21" t="n">
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
         <v>8</v>
       </c>
-      <c r="V21" t="n">
-        <v>6</v>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>@prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
-wd:Q3048624 wd:P1412 wd:Q1860 .
-wd:Q16 wd:P237 wd:Q41549 .
-wd:Q16 wd:P2238 wd:Q81056 .
-wd:Q3048624 wd:P569 wd:Q16 .
-wd:Q16 wd:P122 wd:Q41614 .</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>20</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>1</v>
-      </c>
-      <c r="F22" t="n">
-        <v>2</v>
-      </c>
-      <c r="G22" t="n">
-        <v>1</v>
-      </c>
-      <c r="H22" t="n">
-        <v>1</v>
-      </c>
-      <c r="I22" t="n">
-        <v>1</v>
-      </c>
-      <c r="J22" t="n">
-        <v>1</v>
-      </c>
-      <c r="K22" t="n">
-        <v>1</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>2</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1</v>
-      </c>
-      <c r="S22" t="n">
-        <v>1</v>
-      </c>
-      <c r="T22" t="n">
-        <v>3</v>
-      </c>
-      <c r="U22" t="n">
-        <v>2</v>
-      </c>
-      <c r="V22" t="n">
-        <v>2</v>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>@prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
-&lt;http://www.wikidata.org/entity/Q17052475&gt; &lt;http://www.wikidata.org/entity/P361&gt; &lt;http://www.wikidata.org/entity/Q11348&gt; .
-&lt;http://www.wikidata.org/entity/Q17052475&gt; &lt;http://www.wikidata.org/entity/P361&gt; &lt;http://www.wikidata.org/entity/Q395&gt; .</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>21</v>
-      </c>
-      <c r="B23" t="n">
-        <v>1</v>
-      </c>
-      <c r="C23" t="n">
-        <v>1</v>
-      </c>
-      <c r="D23" t="n">
-        <v>1</v>
-      </c>
-      <c r="E23" t="n">
-        <v>3</v>
-      </c>
-      <c r="F23" t="n">
-        <v>3</v>
-      </c>
-      <c r="G23" t="n">
-        <v>1</v>
-      </c>
-      <c r="H23" t="n">
-        <v>1</v>
-      </c>
-      <c r="I23" t="n">
-        <v>1</v>
-      </c>
-      <c r="J23" t="n">
-        <v>3</v>
-      </c>
-      <c r="K23" t="n">
-        <v>3</v>
-      </c>
-      <c r="L23" t="n">
-        <v>1</v>
-      </c>
-      <c r="M23" t="n">
-        <v>1</v>
-      </c>
-      <c r="N23" t="n">
-        <v>1</v>
-      </c>
-      <c r="O23" t="n">
-        <v>1</v>
-      </c>
-      <c r="P23" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>3</v>
-      </c>
-      <c r="R23" t="n">
-        <v>3</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3</v>
-      </c>
-      <c r="T23" t="n">
-        <v>4</v>
-      </c>
-      <c r="U23" t="n">
-        <v>4</v>
-      </c>
-      <c r="V23" t="n">
-        <v>4</v>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>@prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
-wd:Q18036690 wd:P703 wd:Q15978631 .
-wd:Q18036690 wd:P706 wd:Q430258 .
-wd:Q18036690 wd:P1479 wd:Q12174 .</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>22</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>2</v>
-      </c>
-      <c r="F24" t="n">
-        <v>2</v>
-      </c>
-      <c r="G24" t="n">
-        <v>1</v>
-      </c>
-      <c r="H24" t="n">
-        <v>1</v>
-      </c>
-      <c r="I24" t="n">
-        <v>1</v>
-      </c>
-      <c r="J24" t="n">
-        <v>1</v>
-      </c>
-      <c r="K24" t="n">
-        <v>1</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>2</v>
-      </c>
-      <c r="R24" t="n">
-        <v>2</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2</v>
-      </c>
-      <c r="T24" t="n">
-        <v>3</v>
-      </c>
-      <c r="U24" t="n">
-        <v>3</v>
-      </c>
-      <c r="V24" t="n">
-        <v>3</v>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>@prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
-&lt;http://www.wikidata.org/entity/Q188197&gt; &lt;http://www.wikidata.org/entity/P1346&gt; &lt;http://www.wikidata.org/entity/Q1856183&gt; .
-&lt;http://www.wikidata.org/entity/Q188197&gt; &lt;http://www.wikidata.org/entity/P1346&gt; &lt;http://www.wikidata.org/entity/Q674962&gt; .</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>23</v>
-      </c>
-      <c r="B25" t="n">
-        <v>2</v>
-      </c>
-      <c r="C25" t="n">
-        <v>2</v>
-      </c>
-      <c r="D25" t="n">
-        <v>2</v>
-      </c>
-      <c r="E25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F25" t="n">
-        <v>4</v>
-      </c>
-      <c r="G25" t="n">
-        <v>1</v>
-      </c>
-      <c r="H25" t="n">
-        <v>1</v>
-      </c>
-      <c r="I25" t="n">
-        <v>1</v>
-      </c>
-      <c r="J25" t="n">
-        <v>4</v>
-      </c>
-      <c r="K25" t="n">
-        <v>3</v>
-      </c>
-      <c r="L25" t="n">
-        <v>2</v>
-      </c>
-      <c r="M25" t="n">
-        <v>2</v>
-      </c>
-      <c r="N25" t="n">
-        <v>2</v>
-      </c>
-      <c r="O25" t="n">
-        <v>2</v>
-      </c>
-      <c r="P25" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>4</v>
-      </c>
-      <c r="R25" t="n">
-        <v>3</v>
-      </c>
-      <c r="S25" t="n">
-        <v>3</v>
-      </c>
-      <c r="T25" t="n">
-        <v>5</v>
-      </c>
-      <c r="U25" t="n">
-        <v>4</v>
-      </c>
-      <c r="V25" t="n">
-        <v>4</v>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>@prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
-wd:Q5554167 wd:P31 wd:Q157443 .
-wd:Q5554167 wd:P449 wd:Q220072 .
-wd:Q5554167 wd:P112 wd:Q16239205 .
-wd:Q5554167 wd:P750 wd:Q520445 .</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>24</v>
-      </c>
-      <c r="B26" t="n">
-        <v>0</v>
-      </c>
-      <c r="C26" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" t="n">
-        <v>0</v>
-      </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Error: Error code: 400 - {'object': 'error', 'message': "This model's maximum context length is 8192 tokens. However, you requested 8210 tokens in the messages, Please reduce the length of the messages.", 'type': 'BadRequestError', 'param': None, 'code': 400}
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Error: 3 validation errors for MatchValue
+value.bool
+  Input should be a valid boolean [type=bool_type, input_value=None, input_type=NoneType]
+    For further information visit https://errors.pydantic.dev/2.9/v/bool_type
+value.int
+  Input should be a valid integer [type=int_type, input_value=None, input_type=NoneType]
+    For further information visit https://errors.pydantic.dev/2.9/v/int_type
+value.str
+  Input should be a valid string [type=string_type, input_value=None, input_type=NoneType]
+    For further information visit https://errors.pydantic.dev/2.9/v/string_type
 Traceback:
 Traceback (most recent call last):
   File "/home/mlautenb/CIExMAS/./results/F_URI_Retrieval_Filtering/Gen1v2/slurm/agent_system.py", line 78, in &lt;module&gt;
@@ -2508,42 +1351,1328 @@
   File "/home/mlautenb/miniconda3/envs/CIExMAS/lib/python3.11/site-packages/langgraph/utils/runnable.py", line 371, in invoke
     ret = context.run(self.func, *args, **kwargs)
           ^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^
-  File "/home/mlautenb/CIExMAS/results/F_URI_Retrieval_Filtering/Gen1v2/agents/planner.py", line 31, in agent
-    response = response_chain.invoke(state, config=config)
-               ^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^
-  File "/home/mlautenb/miniconda3/envs/CIExMAS/lib/python3.11/site-packages/langchain_core/runnables/base.py", line 3025, in invoke
-    input = context.run(step.invoke, input, config)
-            ^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^
-  File "/home/mlautenb/miniconda3/envs/CIExMAS/lib/python3.11/site-packages/langchain_core/language_models/chat_models.py", line 307, in invoke
-    self.generate_prompt(
-  File "/home/mlautenb/miniconda3/envs/CIExMAS/lib/python3.11/site-packages/langchain_core/language_models/chat_models.py", line 843, in generate_prompt
-    return self.generate(prompt_messages, stop=stop, callbacks=callbacks, **kwargs)
-           ^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^
-  File "/home/mlautenb/miniconda3/envs/CIExMAS/lib/python3.11/site-packages/langchain_core/language_models/chat_models.py", line 683, in generate
-    self._generate_with_cache(
-  File "/home/mlautenb/miniconda3/envs/CIExMAS/lib/python3.11/site-packages/langchain_core/language_models/chat_models.py", line 908, in _generate_with_cache
-    result = self._generate(
-             ^^^^^^^^^^^^^^^
-  File "/home/mlautenb/miniconda3/envs/CIExMAS/lib/python3.11/site-packages/langchain_openai/chat_models/base.py", line 955, in _generate
-    response = self.client.create(**payload)
-               ^^^^^^^^^^^^^^^^^^^^^^^^^^^^^
-  File "/home/mlautenb/miniconda3/envs/CIExMAS/lib/python3.11/site-packages/openai/_utils/_utils.py", line 279, in wrapper
-    return func(*args, **kwargs)
-           ^^^^^^^^^^^^^^^^^^^^^
-  File "/home/mlautenb/miniconda3/envs/CIExMAS/lib/python3.11/site-packages/openai/resources/chat/completions/completions.py", line 914, in create
-    return self._post(
-           ^^^^^^^^^^^
-  File "/home/mlautenb/miniconda3/envs/CIExMAS/lib/python3.11/site-packages/openai/_base_client.py", line 1242, in post
-    return cast(ResponseT, self.request(cast_to, opts, stream=stream, stream_cls=stream_cls))
-                           ^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^
-  File "/home/mlautenb/miniconda3/envs/CIExMAS/lib/python3.11/site-packages/openai/_base_client.py", line 919, in request
-    return self._request(
-           ^^^^^^^^^^^^^^
-  File "/home/mlautenb/miniconda3/envs/CIExMAS/lib/python3.11/site-packages/openai/_base_client.py", line 1023, in _request
-    raise self._make_status_error_from_response(err.response) from None
-openai.BadRequestError: Error code: 400 - {'object': 'error', 'message': "This model's maximum context length is 8192 tokens. However, you requested 8210 tokens in the messages, Please reduce the length of the messages.", 'type': 'BadRequestError', 'param': None, 'code': 400}
-During task with name 'planner' and id '1e51a1cf-4101-22c4-93d3-517588de8fe6'
+  File "/home/mlautenb/CIExMAS/results/F_URI_Retrieval_Filtering/Gen1v2/agents/uri_retriever.py", line 49, in agent
+    match=models.MatchValue(value="entity" if filter_mode == "Q" else "predicate" if filter_mode == "P" else None)
+          ^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^
+  File "/home/mlautenb/miniconda3/envs/CIExMAS/lib/python3.11/site-packages/pydantic/main.py", line 212, in __init__
+    validated_self = self.__pydantic_validator__.validate_python(data, self_instance=self)
+                     ^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^
+pydantic_core._pydantic_core.ValidationError: 3 validation errors for MatchValue
+value.bool
+  Input should be a valid boolean [type=bool_type, input_value=None, input_type=NoneType]
+    For further information visit https://errors.pydantic.dev/2.9/v/bool_type
+value.int
+  Input should be a valid integer [type=int_type, input_value=None, input_type=NoneType]
+    For further information visit https://errors.pydantic.dev/2.9/v/int_type
+value.str
+  Input should be a valid string [type=string_type, input_value=None, input_type=NoneType]
+    For further information visit https://errors.pydantic.dev/2.9/v/string_type
+During task with name 'uri_retriever_agent' and id '14cf5f2a-ebd5-4e0f-f85a-6745940ea384'
 </t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>914cecf9-f4e5-4272-901c-100fd78d13e6</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="n">
+        <v>2</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" t="n">
+        <v>5</v>
+      </c>
+      <c r="F11" t="n">
+        <v>3</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3</v>
+      </c>
+      <c r="K11" t="n">
+        <v>5</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3</v>
+      </c>
+      <c r="R11" t="n">
+        <v>5</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T11" t="n">
+        <v>5</v>
+      </c>
+      <c r="U11" t="n">
+        <v>6</v>
+      </c>
+      <c r="V11" t="n">
+        <v>5</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>@prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
+wd:Q85563 wd:P26 wd:Q58284 .
+wd:Q24909800 wd:P8045 wd:Q592 .
+wd:Q85563 wd:P3373 wd:Q91204 .</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>7e1b2915-6930-4af8-a1e8-65dbf8a29fb0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>5</v>
+      </c>
+      <c r="F12" t="n">
+        <v>3</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K12" t="n">
+        <v>5</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3</v>
+      </c>
+      <c r="R12" t="n">
+        <v>5</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3</v>
+      </c>
+      <c r="T12" t="n">
+        <v>4</v>
+      </c>
+      <c r="U12" t="n">
+        <v>6</v>
+      </c>
+      <c r="V12" t="n">
+        <v>4</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>@prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
+wd:Q5395743 wd:P37 wd:Q806208 .
+wd:Q5395743 wd:P921 wd:Q735 .
+wd:Q5395743 wd:P1412 wd:Q1321 .</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>bc7ac797-d2f0-4298-afe3-bc194c28baaa</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2</v>
+      </c>
+      <c r="R13" t="n">
+        <v>2</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>3</v>
+      </c>
+      <c r="V13" t="n">
+        <v>3</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>@prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
+&lt;http://www.wikidata.org/entity/Q516760&gt; &lt;http://www.wikidata.org/entity/P585&gt; &lt;http://www.wikidata.org/entity/Q1605654&gt; .
+&lt;http://www.wikidata.org/entity/Q516760&gt; &lt;http://www.wikidata.org/entity/P1344&gt; &lt;http://www.wikidata.org/entity/Q271108&gt; .</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>2ef90b90-8a8e-4a10-baea-3e067a2ed316</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" t="n">
+        <v>4</v>
+      </c>
+      <c r="G14" t="n">
+        <v>3</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2</v>
+      </c>
+      <c r="J14" t="n">
+        <v>4</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>4</v>
+      </c>
+      <c r="R14" t="n">
+        <v>3</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2</v>
+      </c>
+      <c r="T14" t="n">
+        <v>5</v>
+      </c>
+      <c r="U14" t="n">
+        <v>3</v>
+      </c>
+      <c r="V14" t="n">
+        <v>3</v>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>@prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
+wd:Q7992209 wd:P112 wd:Q3561541 .
+wd:Q5364109 wd:P361 wd:Q204442 .
+wd:Q3561541 wd:P31 wd:Q40218 .
+wd:Q3561541 wd:P200 wd:Q5364109 .</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>da6107d0-c2dd-4de5-a31b-5b943d714d56</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="n">
+        <v>2</v>
+      </c>
+      <c r="C15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" t="n">
+        <v>4</v>
+      </c>
+      <c r="F15" t="n">
+        <v>4</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" t="n">
+        <v>4</v>
+      </c>
+      <c r="K15" t="n">
+        <v>4</v>
+      </c>
+      <c r="L15" t="n">
+        <v>3</v>
+      </c>
+      <c r="M15" t="n">
+        <v>3</v>
+      </c>
+      <c r="N15" t="n">
+        <v>3</v>
+      </c>
+      <c r="O15" t="n">
+        <v>3</v>
+      </c>
+      <c r="P15" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>4</v>
+      </c>
+      <c r="R15" t="n">
+        <v>4</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2</v>
+      </c>
+      <c r="T15" t="n">
+        <v>5</v>
+      </c>
+      <c r="U15" t="n">
+        <v>5</v>
+      </c>
+      <c r="V15" t="n">
+        <v>3</v>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>@prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
+wd:Q42916999 wd:P361 wd:Q568973 .
+wd:Q42916999 wd:P31 wd:Q28221935 .
+wd:Q42916999 wd:P530 wd:Q183 .
+wd:Q42916999 wd:P155 wd:Q794186 .</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>90c07b6f-999a-49e9-b823-6df307c9038d</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2</v>
+      </c>
+      <c r="V16" t="n">
+        <v>2</v>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>@prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
+wd:Q3311362 wd:P131 wd:Q66117 .
+wd:Q3311362 wd:P131 wd:Q66117 .</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>1e71e957-733b-4430-9963-c5e0603f6d61</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="n">
+        <v>3</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2</v>
+      </c>
+      <c r="R17" t="n">
+        <v>3</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>4</v>
+      </c>
+      <c r="V17" t="n">
+        <v>3</v>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>@prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
+wd:Q7044514 wd:P175 wd:Q234199 .
+wd:Q7044514 wd:P527 wd:Q46046 .</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>95ac2a88-7176-4aa6-9b3a-02f48fe42afc</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="n">
+        <v>3</v>
+      </c>
+      <c r="C18" t="n">
+        <v>3</v>
+      </c>
+      <c r="D18" t="n">
+        <v>3</v>
+      </c>
+      <c r="E18" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" t="n">
+        <v>3</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3</v>
+      </c>
+      <c r="L18" t="n">
+        <v>3</v>
+      </c>
+      <c r="M18" t="n">
+        <v>3</v>
+      </c>
+      <c r="N18" t="n">
+        <v>3</v>
+      </c>
+      <c r="O18" t="n">
+        <v>3</v>
+      </c>
+      <c r="P18" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3</v>
+      </c>
+      <c r="R18" t="n">
+        <v>3</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3</v>
+      </c>
+      <c r="T18" t="n">
+        <v>4</v>
+      </c>
+      <c r="U18" t="n">
+        <v>4</v>
+      </c>
+      <c r="V18" t="n">
+        <v>4</v>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>@prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
+wd:Q607380 wd:P5588 wd:Q782 .
+wd:Q607380 wd:P183 wd:Q664 .
+wd:Q607380 wd:P1672 wd:Q6933370 .</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>3408f680-bb43-4475-8f2a-30e92961f0fc</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="n">
+        <v>3</v>
+      </c>
+      <c r="C19" t="n">
+        <v>4</v>
+      </c>
+      <c r="D19" t="n">
+        <v>4</v>
+      </c>
+      <c r="E19" t="n">
+        <v>4</v>
+      </c>
+      <c r="F19" t="n">
+        <v>4</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3</v>
+      </c>
+      <c r="L19" t="n">
+        <v>2</v>
+      </c>
+      <c r="M19" t="n">
+        <v>3</v>
+      </c>
+      <c r="N19" t="n">
+        <v>3</v>
+      </c>
+      <c r="O19" t="n">
+        <v>3</v>
+      </c>
+      <c r="P19" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>4</v>
+      </c>
+      <c r="R19" t="n">
+        <v>4</v>
+      </c>
+      <c r="S19" t="n">
+        <v>4</v>
+      </c>
+      <c r="T19" t="n">
+        <v>5</v>
+      </c>
+      <c r="U19" t="n">
+        <v>5</v>
+      </c>
+      <c r="V19" t="n">
+        <v>5</v>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>@prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
+&lt;http://www.wikidata.org/entity/Q5686841&gt; &lt;http://www.wikidata.org/entity/P361&gt; &lt;http://www.wikidata.org/entity/Q794&gt; .
+&lt;http://www.wikidata.org/entity/Q5686841&gt; &lt;http://www.wikidata.org/entity/P1012&gt; &lt;http://www.wikidata.org/entity/Q308864&gt; .
+&lt;http://www.wikidata.org/entity/Q5686841&gt; &lt;http://www.wikidata.org/entity/P1012&gt; &lt;http://www.wikidata.org/entity/Q928828&gt; .
+&lt;http://www.wikidata.org/entity/Q308864&gt; &lt;http://www.wikidata.org/entity/P150&gt; &lt;http://www.wikidata.org/entity/Q1282219&gt; .</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>e11b2551-507d-453c-8ec9-9ac2614a96f2</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
+      </c>
+      <c r="V20" t="n">
+        <v>2</v>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>@prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
+&lt;http://www.wikidata.org/entity/Q20671544&gt; &lt;http://www.wikidata.org/entity/P527&gt; &lt;http://www.wikidata.org/entity/Q27914&gt; .</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>b62959c0-51aa-41d0-9ca1-26dafe1860e4</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="n">
+        <v>5</v>
+      </c>
+      <c r="C21" t="n">
+        <v>5</v>
+      </c>
+      <c r="D21" t="n">
+        <v>5</v>
+      </c>
+      <c r="E21" t="n">
+        <v>7</v>
+      </c>
+      <c r="F21" t="n">
+        <v>6</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J21" t="n">
+        <v>6</v>
+      </c>
+      <c r="K21" t="n">
+        <v>7</v>
+      </c>
+      <c r="L21" t="n">
+        <v>6</v>
+      </c>
+      <c r="M21" t="n">
+        <v>6</v>
+      </c>
+      <c r="N21" t="n">
+        <v>6</v>
+      </c>
+      <c r="O21" t="n">
+        <v>6</v>
+      </c>
+      <c r="P21" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>6</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="n">
+        <v>6</v>
+      </c>
+      <c r="U21" t="n">
+        <v>8</v>
+      </c>
+      <c r="V21" t="n">
+        <v>6</v>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>@prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
+wd:Q16 wd:P237 wd:Q41549 .
+wd:Q3048624 wd:P1412 wd:Q1860 .
+wd:Q3048624 wd:P27 wd:Q16 .
+wd:Q16 wd:P122 wd:Q41614 .
+wd:Q16 wd:P2238 wd:Q81056 .
+wd:Q3048624 wd:P106 wd:Q3048624 .
+wd:Q3048624 wd:P1412 wd:Q1860 .</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>9bd216ef-c81c-47fb-9822-a6daff5d6b74</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1</v>
+      </c>
+      <c r="N22" t="n">
+        <v>1</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
+      </c>
+      <c r="V22" t="n">
+        <v>2</v>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>@prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
+wd:Q17052475 wd:P279 wd:Q11348 .</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>dc292ef2-7836-46f7-be3e-dc4a58738c0b</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" t="n">
+        <v>3</v>
+      </c>
+      <c r="F23" t="n">
+        <v>3</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" t="n">
+        <v>3</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1</v>
+      </c>
+      <c r="N23" t="n">
+        <v>1</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>3</v>
+      </c>
+      <c r="R23" t="n">
+        <v>3</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3</v>
+      </c>
+      <c r="T23" t="n">
+        <v>4</v>
+      </c>
+      <c r="U23" t="n">
+        <v>4</v>
+      </c>
+      <c r="V23" t="n">
+        <v>4</v>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>@prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
+&lt;http://www.wikidata.org/entity/Q18036690&gt; &lt;http://www.wikidata.org/entity/P703&gt; &lt;http://www.wikidata.org/entity/Q15978631&gt; .
+&lt;http://www.wikidata.org/entity/Q18036690&gt; &lt;http://www.wikidata.org/entity/P1479&gt; &lt;http://www.wikidata.org/entity/Q12174&gt; .
+&lt;http://www.wikidata.org/entity/Q18036690&gt; &lt;http://www.wikidata.org/entity/P706&gt; &lt;http://www.wikidata.org/entity/Q430258&gt; .</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>26b40ff2-87cf-4a07-b1a6-b66b0dd90442</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="n">
+        <v>2</v>
+      </c>
+      <c r="C24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2</v>
+      </c>
+      <c r="E24" t="n">
+        <v>2</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1</v>
+      </c>
+      <c r="N24" t="n">
+        <v>1</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2</v>
+      </c>
+      <c r="R24" t="n">
+        <v>2</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3</v>
+      </c>
+      <c r="U24" t="n">
+        <v>3</v>
+      </c>
+      <c r="V24" t="n">
+        <v>3</v>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>@prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
+&lt;http://www.wikidata.org/entity/Q188197&gt; &lt;http://www.wikidata.org/entity/P2522&gt; &lt;http://www.wikidata.org/entity/Q674962&gt; .
+&lt;http://www.wikidata.org/entity/Q188197&gt; &lt;http://www.wikidata.org/entity/P2522&gt; &lt;http://www.wikidata.org/entity/Q1856183&gt; .</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>c0871eaa-c255-453a-a01d-d075e8f51d7b</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="n">
+        <v>2</v>
+      </c>
+      <c r="C25" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2</v>
+      </c>
+      <c r="E25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F25" t="n">
+        <v>3</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" t="n">
+        <v>3</v>
+      </c>
+      <c r="K25" t="n">
+        <v>3</v>
+      </c>
+      <c r="L25" t="n">
+        <v>2</v>
+      </c>
+      <c r="M25" t="n">
+        <v>2</v>
+      </c>
+      <c r="N25" t="n">
+        <v>2</v>
+      </c>
+      <c r="O25" t="n">
+        <v>2</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>3</v>
+      </c>
+      <c r="R25" t="n">
+        <v>3</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3</v>
+      </c>
+      <c r="T25" t="n">
+        <v>4</v>
+      </c>
+      <c r="U25" t="n">
+        <v>4</v>
+      </c>
+      <c r="V25" t="n">
+        <v>4</v>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>@prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
+&lt;http://www.wikidata.org/entity/Q5554167&gt; &lt;http://www.wikidata.org/entity/P86&gt; &lt;http://www.wikidata.org/entity/Q16239205&gt; .
+&lt;http://www.wikidata.org/entity/Q5554167&gt; &lt;http://www.wikidata.org/entity/P750&gt; &lt;http://www.wikidata.org/entity/Q520445&gt; .
+&lt;http://www.wikidata.org/entity/Q5554167&gt; &lt;http://www.wikidata.org/entity/Q1225307&gt; &lt;http://www.wikidata.org/entity/Q220072&gt; .</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>b5138a9e-e529-4f10-97ac-4a9291b592b3</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="n">
+        <v>2</v>
+      </c>
+      <c r="C26" t="n">
+        <v>2</v>
+      </c>
+      <c r="D26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E26" t="n">
+        <v>7</v>
+      </c>
+      <c r="F26" t="n">
+        <v>7</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" t="n">
+        <v>2</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" t="n">
+        <v>4</v>
+      </c>
+      <c r="K26" t="n">
+        <v>4</v>
+      </c>
+      <c r="L26" t="n">
+        <v>2</v>
+      </c>
+      <c r="M26" t="n">
+        <v>2</v>
+      </c>
+      <c r="N26" t="n">
+        <v>2</v>
+      </c>
+      <c r="O26" t="n">
+        <v>2</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>7</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7</v>
+      </c>
+      <c r="S26" t="n">
+        <v>6</v>
+      </c>
+      <c r="T26" t="n">
+        <v>8</v>
+      </c>
+      <c r="U26" t="n">
+        <v>7</v>
+      </c>
+      <c r="V26" t="n">
+        <v>7</v>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>@prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
+wd:Q62066211 wd:P941 wd:Q486296 .
+wd:Q62066211 wd:P941 wd:Q698752 .
+wd:Q62066211 &lt;http://www.wikidata.org/entity/P533&gt; wd:Q62066735 .
+wd:Q62066211 wd:P793 wd:Q664 .
+wd:Q62066211 wd:P1535 wd:Q11244 .
+wd:Q62066211 wd:P1535 wd:Q486396 .
+wd:Q62066211 &lt;http://www.wikidata.org/entity/P533&gt; wd:Q62066751 .</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>14b2fa30-5508-4c87-b305-6da3c8fdd524</t>
         </is>
       </c>
     </row>
@@ -2552,19 +2681,19 @@
         <v>25</v>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E27" t="n">
         <v>4</v>
       </c>
       <c r="F27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G27" t="n">
         <v>2</v>
@@ -2576,28 +2705,28 @@
         <v>2</v>
       </c>
       <c r="J27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K27" t="n">
         <v>4</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R27" t="n">
         <v>4</v>
@@ -2606,7 +2735,7 @@
         <v>2</v>
       </c>
       <c r="T27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U27" t="n">
         <v>5</v>
@@ -2617,8 +2746,14 @@
       <c r="W27" t="inlineStr">
         <is>
           <t>@prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
-wd:Q2094579 wd:P287 wd:Q5546527 .
-wd:Q5546527 wd:P138 wd:Q8229 .</t>
+wd:Q2094579 wd:P50 wd:Q5546527 .
+wd:Q5546527 wd:P735 "George" .
+wd:Q2094579 wd:P162 wd:Q827379 .</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>d17d8582-70d4-4ea8-b275-615f8ab8c7aa</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2774,7 @@
         <v>2</v>
       </c>
       <c r="F28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G28" t="n">
         <v>2</v>
@@ -2651,7 +2786,7 @@
         <v>2</v>
       </c>
       <c r="J28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K28" t="n">
         <v>2</v>
@@ -2672,7 +2807,7 @@
         <v>2</v>
       </c>
       <c r="Q28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R28" t="n">
         <v>2</v>
@@ -2681,7 +2816,7 @@
         <v>2</v>
       </c>
       <c r="T28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U28" t="n">
         <v>3</v>
@@ -2692,9 +2827,13 @@
       <c r="W28" t="inlineStr">
         <is>
           <t>@prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
-&lt;http://www.wikidata.org/entity/Q22082365&gt; &lt;http://www.wikidata.org/entity/P527&gt; &lt;http://www.wikidata.org/entity/Q3957&gt; .
-&lt;http://www.wikidata.org/entity/Q965&gt; &lt;http://www.wikidata.org/entity/P463&gt; &lt;http://www.wikidata.org/entity/Q47543&gt; .
-&lt;http://www.wikidata.org/entity/Q22082365&gt; &lt;http://www.wikidata.org/entity/P131&gt; &lt;http://www.wikidata.org/entity/Q965&gt; .</t>
+&lt;http://www.wikidata.org/entity/Q22082365&gt; &lt;http://www.wikidata.org/entity/P131&gt; &lt;http://www.wikidata.org/entity/Q965&gt; .
+&lt;http://www.wikidata.org/entity/Q965&gt; &lt;http://www.wikidata.org/entity/P463&gt; &lt;http://www.wikidata.org/entity/Q47543&gt; .</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>4300f974-d01f-4658-a10e-beb83ab3b525</t>
         </is>
       </c>
     </row>
@@ -2703,28 +2842,28 @@
         <v>27</v>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E29" t="n">
         <v>4</v>
       </c>
       <c r="F29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G29" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H29" t="n">
         <v>1</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J29" t="n">
         <v>3</v>
@@ -2733,28 +2872,28 @@
         <v>3</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R29" t="n">
         <v>4</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T29" t="n">
         <v>5</v>
@@ -2763,16 +2902,21 @@
         <v>5</v>
       </c>
       <c r="V29" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="W29" t="inlineStr">
         <is>
           <t>@prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
-wd:Q6811747 wd:P31 wd:Q685 .
-wd:Q408 wd:P131 wd:Q685 .
-wd:Q6762533 wd:P131 wd:Q408 .
-wd:Q8062829 wd:P137 wd:Q685 .
-wd:Q6762533 wd:P131 wd:Q408 .</t>
+wd:Q16926803 wd:P137 wd:Q8062829 .
+wd:Q8062829 wd:P137 wd:Q2060470 .
+wd:Q16926803 wd:P609 wd:Q6811747 .
+wd:Q16926803 wd:P609 wd:Q6762533 .
+wd:Q16926803 wd:P1535 wd:Q8062829 .</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>73949889-df33-42fd-9b21-20a3c208bd28</t>
         </is>
       </c>
     </row>
@@ -2781,127 +2925,80 @@
         <v>28</v>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error: Error code: 400 - {'object': 'error', 'message': "This model's maximum context length is 8192 tokens. However, you requested 8201 tokens in the messages, Please reduce the length of the messages.", 'type': 'BadRequestError', 'param': None, 'code': 400}
-Traceback:
-Traceback (most recent call last):
-  File "/home/mlautenb/CIExMAS/./results/F_URI_Retrieval_Filtering/Gen1v2/slurm/agent_system.py", line 78, in &lt;module&gt;
-    response = graph.invoke({
-               ^^^^^^^^^^^^^^
-  File "/home/mlautenb/miniconda3/envs/CIExMAS/lib/python3.11/site-packages/langgraph/pregel/__init__.py", line 2683, in invoke
-    for chunk in self.stream(
-  File "/home/mlautenb/miniconda3/envs/CIExMAS/lib/python3.11/site-packages/langgraph/pregel/__init__.py", line 2331, in stream
-    for _ in runner.tick(
-  File "/home/mlautenb/miniconda3/envs/CIExMAS/lib/python3.11/site-packages/langgraph/pregel/runner.py", line 146, in tick
-    run_with_retry(
-  File "/home/mlautenb/miniconda3/envs/CIExMAS/lib/python3.11/site-packages/langgraph/pregel/retry.py", line 40, in run_with_retry
-    return task.proc.invoke(task.input, config)
-           ^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^
-  File "/home/mlautenb/miniconda3/envs/CIExMAS/lib/python3.11/site-packages/langgraph/utils/runnable.py", line 606, in invoke
-    input = step.invoke(input, config, **kwargs)
-            ^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^
-  File "/home/mlautenb/miniconda3/envs/CIExMAS/lib/python3.11/site-packages/langgraph/utils/runnable.py", line 371, in invoke
-    ret = context.run(self.func, *args, **kwargs)
-          ^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^
-  File "/home/mlautenb/CIExMAS/results/F_URI_Retrieval_Filtering/Gen1v2/agents/planner.py", line 31, in agent
-    response = response_chain.invoke(state, config=config)
-               ^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^
-  File "/home/mlautenb/miniconda3/envs/CIExMAS/lib/python3.11/site-packages/langchain_core/runnables/base.py", line 3025, in invoke
-    input = context.run(step.invoke, input, config)
-            ^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^
-  File "/home/mlautenb/miniconda3/envs/CIExMAS/lib/python3.11/site-packages/langchain_core/language_models/chat_models.py", line 307, in invoke
-    self.generate_prompt(
-  File "/home/mlautenb/miniconda3/envs/CIExMAS/lib/python3.11/site-packages/langchain_core/language_models/chat_models.py", line 843, in generate_prompt
-    return self.generate(prompt_messages, stop=stop, callbacks=callbacks, **kwargs)
-           ^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^
-  File "/home/mlautenb/miniconda3/envs/CIExMAS/lib/python3.11/site-packages/langchain_core/language_models/chat_models.py", line 683, in generate
-    self._generate_with_cache(
-  File "/home/mlautenb/miniconda3/envs/CIExMAS/lib/python3.11/site-packages/langchain_core/language_models/chat_models.py", line 908, in _generate_with_cache
-    result = self._generate(
-             ^^^^^^^^^^^^^^^
-  File "/home/mlautenb/miniconda3/envs/CIExMAS/lib/python3.11/site-packages/langchain_openai/chat_models/base.py", line 955, in _generate
-    response = self.client.create(**payload)
-               ^^^^^^^^^^^^^^^^^^^^^^^^^^^^^
-  File "/home/mlautenb/miniconda3/envs/CIExMAS/lib/python3.11/site-packages/openai/_utils/_utils.py", line 279, in wrapper
-    return func(*args, **kwargs)
-           ^^^^^^^^^^^^^^^^^^^^^
-  File "/home/mlautenb/miniconda3/envs/CIExMAS/lib/python3.11/site-packages/openai/resources/chat/completions/completions.py", line 914, in create
-    return self._post(
-           ^^^^^^^^^^^
-  File "/home/mlautenb/miniconda3/envs/CIExMAS/lib/python3.11/site-packages/openai/_base_client.py", line 1242, in post
-    return cast(ResponseT, self.request(cast_to, opts, stream=stream, stream_cls=stream_cls))
-                           ^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^
-  File "/home/mlautenb/miniconda3/envs/CIExMAS/lib/python3.11/site-packages/openai/_base_client.py", line 919, in request
-    return self._request(
-           ^^^^^^^^^^^^^^
-  File "/home/mlautenb/miniconda3/envs/CIExMAS/lib/python3.11/site-packages/openai/_base_client.py", line 1023, in _request
-    raise self._make_status_error_from_response(err.response) from None
-openai.BadRequestError: Error code: 400 - {'object': 'error', 'message': "This model's maximum context length is 8192 tokens. However, you requested 8201 tokens in the messages, Please reduce the length of the messages.", 'type': 'BadRequestError', 'param': None, 'code': 400}
-During task with name 'planner' and id 'a2ad5b5f-1d98-d2bc-d71a-3051637d8ae5'
-</t>
+          <t>@prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
+wd:Q8083051 wd:P131 wd:Q36 .
+wd:Q8083051 wd:P131 wd:Q1840968 .
+wd:Q8083051 wd:P131 wd:Q6723 .
+wd:Q8083051 wd:P131 wd:Q6655 .</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>1100ea62-e6e5-4d24-9613-aa8806333713</t>
         </is>
       </c>
     </row>
@@ -2910,19 +3007,19 @@
         <v>29</v>
       </c>
       <c r="B31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E31" t="n">
         <v>3</v>
       </c>
       <c r="F31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G31" t="n">
         <v>3</v>
@@ -2955,7 +3052,7 @@
         <v>2</v>
       </c>
       <c r="Q31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R31" t="n">
         <v>3</v>
@@ -2964,7 +3061,7 @@
         <v>3</v>
       </c>
       <c r="T31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U31" t="n">
         <v>4</v>
@@ -2976,11 +3073,16 @@
         <is>
           <t>@prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
 wd:Q14707624 wd:P1408 wd:Q304801 .
-wd:Q14707624 wd:P131 wd:Q304801 .
-wd:Q14707624 wd:P131 wd:Q1384 .
+wd:Q1384 wd:P131 wd:Q30 .
+wd:Q14707624 wd:P1408 wd:Q304801 .
+wd:Q14707624 wd:P131 wd:304801 .
 wd:Q304801 wd:P131 wd:Q1384 .
-wd:Q1384 wd:P131 wd:Q30 .
 wd:Q304801 wd:P131 wd:Q1384 .</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>4f46581c-98e5-464e-9e2b-2bc426faf607</t>
         </is>
       </c>
     </row>
@@ -2995,7 +3097,7 @@
         <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E32" t="n">
         <v>2</v>
@@ -3028,10 +3130,10 @@
         <v>2</v>
       </c>
       <c r="O32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q32" t="n">
         <v>3</v>
@@ -3054,9 +3156,14 @@
       <c r="W32" t="inlineStr">
         <is>
           <t>@prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
-wd:Q64876878 wd:P674 wd:Q65090308 .
-wd:Q65090308 wd:P674 wd:Q64876878 .
-wd:Q64876878 wd:P725 wd:Q262170 .</t>
+&lt;http://www.wikidata.org/entity/Q65090308&gt; &lt;http://www.wikidata.org/entity/P161&gt; &lt;http://www.wikidata.org/entity/Q64876878&gt; .
+&lt;http://www.wikidata.org/entity/Q64876878&gt; &lt;http://www.wikidata.org/entity/P161&gt; &lt;http://www.wikidata.org/entity/Q65090308&gt; .
+&lt;http://www.wikidata.org/entity/Q64876878&gt; &lt;http://www.wikidata.org/entity/P725&gt; &lt;http://www.wikidata.org/entity/Q262170&gt; .</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>37376e8e-736e-457e-9195-9adf7498a3b2</t>
         </is>
       </c>
     </row>
@@ -3065,7 +3172,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C33" t="n">
         <v>2</v>
@@ -3080,13 +3187,13 @@
         <v>5</v>
       </c>
       <c r="G33" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H33" t="n">
         <v>3</v>
       </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J33" t="n">
         <v>3</v>
@@ -3104,10 +3211,10 @@
         <v>3</v>
       </c>
       <c r="O33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q33" t="n">
         <v>4</v>
@@ -3119,22 +3226,28 @@
         <v>4</v>
       </c>
       <c r="T33" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U33" t="n">
         <v>7</v>
       </c>
       <c r="V33" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W33" t="inlineStr">
         <is>
           <t>@prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
-&lt;http://www.wikidata.org/entity/Q1240173&gt; &lt;http://www.wikidata.org/entity/P460&gt; &lt;http://www.wikidata.org/entity/Q2722661&gt; .
-&lt;http://www.wikidata.org/entity/Q1240173&gt; &lt;http://www.wikidata.org/entity/P131&gt; &lt;http://www.wikidata.org/entity/Q1088790&gt; .
-&lt;http://www.wikidata.org/entity/Q1240173&gt; &lt;http://www.wikidata.org/entity/P131&gt; &lt;http://www.wikidata.org/entity/Q190518&gt; .
-&lt;http://www.wikidata.org/entity/Q1240173&gt; &lt;http://www.wikidata.org/entity/P131&gt; &lt;http://www.wikidata.org/entity/Q28&gt; .
-&lt;http://www.wikidata.org/entity/Q1240173&gt; &lt;http://www.wikidata.org/entity/P149&gt; &lt;http://www.wikidata.org/entity/Q2722661&gt; .</t>
+wd:Q190518 wd:P361 wd:Q28 .
+wd:Q46261 wd:P361 wd:Q2722661 .
+wd:Q1088790 wd:P361 wd:Q28 .
+wd:Q1240173 wd:P131 wd:Q1088790 .
+wd:Q1240173 wd:P149 wd:Q46261 .
+wd:Q46261 wd:P361 wd:Q2722661 .</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>520dae9a-3cae-49c6-88a0-004dd3c87755</t>
         </is>
       </c>
     </row>
@@ -3143,13 +3256,13 @@
         <v>32</v>
       </c>
       <c r="B34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E34" t="n">
         <v>3</v>
@@ -3173,19 +3286,19 @@
         <v>3</v>
       </c>
       <c r="L34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q34" t="n">
         <v>3</v>
@@ -3208,9 +3321,14 @@
       <c r="W34" t="inlineStr">
         <is>
           <t>@prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
+wd:Q822946 wd:P674 wd:Q1366759 .
 wd:Q822946 wd:P2408 wd:Q2644 .
-wd:Q822946 wd:P161 wd:Q1366759 .
 wd:Q822946 wd:P361 wd:Q130232 .</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>b2b8d32d-ecb5-45bb-833c-a3f1ad98462a</t>
         </is>
       </c>
     </row>
@@ -3231,19 +3349,19 @@
         <v>1</v>
       </c>
       <c r="F35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H35" t="n">
         <v>1</v>
       </c>
       <c r="I35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K35" t="n">
         <v>1</v>
@@ -3284,9 +3402,13 @@
       <c r="W35" t="inlineStr">
         <is>
           <t>@prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
-wd:Q41792848 wd:P287 wd:Q5072388 .
-wd:Q41792848 wd:P361 wd:Q41792848 .
-wd:Q5072388 wd:P1441 wd:Q41792848 .</t>
+wd:Q41792848 wd:P106 wd:Q41792848 .
+wd:Q41792848 wd:P287 wd:Q5072388 .</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>91136111-c6da-4c55-94f3-77ca4d110004</t>
         </is>
       </c>
     </row>
@@ -3295,19 +3417,19 @@
         <v>34</v>
       </c>
       <c r="B36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E36" t="n">
         <v>2</v>
       </c>
       <c r="F36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G36" t="n">
         <v>1</v>
@@ -3319,48 +3441,54 @@
         <v>1</v>
       </c>
       <c r="J36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K36" t="n">
         <v>2</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R36" t="n">
         <v>2</v>
       </c>
       <c r="S36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U36" t="n">
         <v>3</v>
       </c>
       <c r="V36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W36" t="inlineStr">
         <is>
           <t>@prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
-wd:Q1490434 wd:P361 wd:Q41298 .</t>
+&lt;http://www.wikidata.org/entity/Q1490434&gt; &lt;http://www.wikidata.org/entity/P31&gt; &lt;http://www.wikidata.org/entity/Q41298&gt; .
+&lt;http://www.wikidata.org/entity/Q1490434&gt; &lt;http://www.wikidata.org/entity/P131&gt; &lt;http://www.wikidata.org/entity/Q183&gt; .</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>a1def812-386b-49ae-91ad-a81d63d32167</t>
         </is>
       </c>
     </row>
@@ -3408,10 +3536,10 @@
         <v>1</v>
       </c>
       <c r="O37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q37" t="n">
         <v>3</v>
@@ -3435,8 +3563,13 @@
         <is>
           <t>@prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
 wd:Q2616869 wd:P1433 wd:Q1126800 .
-wd:Q2616869 wd:P460 wd:Q132311 .
-wd:Q2616869 wd:P361 wd:Q19652 .</t>
+wd:Q2616869 wd:Q2644 wd:Q132311 .
+wd:Q2616869 wd:P1552 wd:Q19652 .</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>31da8879-308b-4494-aaae-3b4ff9c437b4</t>
         </is>
       </c>
     </row>
@@ -3448,16 +3581,16 @@
         <v>0</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E38" t="n">
         <v>4</v>
       </c>
       <c r="F38" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G38" t="n">
         <v>3</v>
@@ -3510,11 +3643,17 @@
       <c r="W38" t="inlineStr">
         <is>
           <t>@prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
-wd:Q6803534 wd:P31 wd:Q1320721 .
+wd:Q6803534 wd:P527 wd:Q1320721 .
+wd:Q6803534 wd:P131 wd:Q145 .
+wd:Q6803534 wd:P131 wd:Q1084560 .
 wd:Q1247390 wd:P361 wd:Q145 .
-wd:Q6803534 wd:P131 wd:Q1247390 .
-wd:Q6803534 wd:P131 wd:Q1084560 .
-wd:Q1084560 wd:P361 wd:Q1247390 .</t>
+wd:Q1084560 wd:P361 wd:Q145 .
+wd:Q6803534 wd:P131 wd:Q1247390 .</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>2484e076-e355-42ab-9e0e-2e056360c612</t>
         </is>
       </c>
     </row>
@@ -3588,8 +3727,13 @@
       <c r="W39" t="inlineStr">
         <is>
           <t>@prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
-wd:Q907827 wd:P131 wd:Q183 .
-wd:Q907827 wd:P1546 wd:Q877781 .</t>
+wd:Q907827 wd:P1552 wd:Q877781 .
+wd:Q907827 wd:P3842 wd:Q183 .</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>3df5f777-3ff2-4252-a6f7-2bf19acdafa0</t>
         </is>
       </c>
     </row>
@@ -3598,7 +3742,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C40" t="n">
         <v>1</v>
@@ -3610,7 +3754,7 @@
         <v>1</v>
       </c>
       <c r="F40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G40" t="n">
         <v>1</v>
@@ -3622,13 +3766,13 @@
         <v>1</v>
       </c>
       <c r="J40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K40" t="n">
         <v>1</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M40" t="n">
         <v>1</v>
@@ -3637,13 +3781,13 @@
         <v>1</v>
       </c>
       <c r="O40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R40" t="n">
         <v>1</v>
@@ -3663,9 +3807,13 @@
       <c r="W40" t="inlineStr">
         <is>
           <t>@prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
-wd:Q1064344 wd:P361 wd:Q1406 .
-wd:Q1064344 wd:P279 wd:Q1406 .
-wd:Q1064344 wd:P527 wd:Q1064344 .</t>
+&lt;http://www.wikidata.org/entity/Q1064344&gt; &lt;http://www.wikidata.org/entity/P361&gt; &lt;http://www.wikidata.org/entity/Q1406&gt; .
+&lt;http://www.wikidata.org/entity/Q1064344&gt; &lt;http://www.wikidata.org/entity/P179&gt; &lt;http://www.wikidata.org/entity/Q1406&gt; .</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>47d8e9fa-42d6-4891-bf7f-8b5b50898171</t>
         </is>
       </c>
     </row>
@@ -3674,13 +3822,13 @@
         <v>39</v>
       </c>
       <c r="B41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E41" t="n">
         <v>2</v>
@@ -3704,19 +3852,19 @@
         <v>2</v>
       </c>
       <c r="L41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q41" t="n">
         <v>2</v>
@@ -3739,8 +3887,13 @@
       <c r="W41" t="inlineStr">
         <is>
           <t>@prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
-&lt;http://www.wikidata.org/entity/Q47554&gt; &lt;http://www.wikidata.org/entity/P1376&gt; &lt;http://www.wikidata.org/entity/Q54153&gt; .
-&lt;http://www.wikidata.org/entity/Q47554&gt; &lt;http://www.wikidata.org/entity/P706&gt; &lt;http://www.wikidata.org/entity/Q1261531&gt; .</t>
+&lt;http://www.wikidata.org/entity/Q47554&gt; &lt;http://www.wikidata.org/entity/P206&gt; &lt;http://www.wikidata.org/entity/Q1261531&gt; .
+&lt;http://www.wikidata.org/entity/Q47554&gt; &lt;http://www.wikidata.org/entity/P1376&gt; &lt;http://www.wikidata.org/entity/Q54153&gt; .</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>a9e0be8a-9d6a-427a-9bf7-ad2ec86d3edd</t>
         </is>
       </c>
     </row>
@@ -3761,7 +3914,7 @@
         <v>6</v>
       </c>
       <c r="F42" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G42" t="n">
         <v>2</v>
@@ -3794,33 +3947,36 @@
         <v>3</v>
       </c>
       <c r="Q42" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R42" t="n">
         <v>6</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U42" t="n">
         <v>7</v>
       </c>
       <c r="V42" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W42" t="inlineStr">
         <is>
           <t>@prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
-wd:Q54322348 wd:P131 wd:Q16568 .
+wd:Q16568 wd:P190 wd:Q12191 .
+wd:Q16568 wd:P190 wd:Q42622 .
+wd:Q16568 wd:P131 wd:Q116 .
 wd:Q16568 wd:P1376 wd:Q493605 .
-wd:Q16568 wd:P131 wd:Q30 .
-wd:Q54322348 wd:P131 wd:Q16568 .
-wd:Q16568 wd:P190 wd:Q42622 .
-wd:Q16568 wd:P190 wd:Q12191 .
-wd:Q16568 wd:P131 wd:Q11696 .</t>
+wd:Q54322348 wd:P131 wd:Q16568 .</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>00c44f64-5975-445d-bb7b-5ff7bbe40b5d</t>
         </is>
       </c>
     </row>
@@ -3894,8 +4050,13 @@
       <c r="W43" t="inlineStr">
         <is>
           <t>@prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
-wd:Q87412161 wd:P3373 wd:Q95994024 .
-wd:Q87412161 wd:P31 wd:Q5 .</t>
+&lt;http://www.wikidata.org/entity/Q87412161&gt; &lt;http://www.wikidata.org/entity/P31&gt; &lt;http://www.wikidata.org/entity/Q5&gt; .
+&lt;http://www.wikidata.org/entity/Q87412161&gt; &lt;http://www.wikidata.org/entity/P3373&gt; &lt;http://www.wikidata.org/entity/Q95994024&gt; .</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>93ee912f-457a-4172-be33-d18db17e4889</t>
         </is>
       </c>
     </row>
@@ -3916,10 +4077,10 @@
         <v>2</v>
       </c>
       <c r="F44" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H44" t="n">
         <v>1</v>
@@ -3928,7 +4089,7 @@
         <v>1</v>
       </c>
       <c r="J44" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K44" t="n">
         <v>2</v>
@@ -3949,7 +4110,7 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R44" t="n">
         <v>2</v>
@@ -3958,7 +4119,7 @@
         <v>2</v>
       </c>
       <c r="T44" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U44" t="n">
         <v>3</v>
@@ -3969,9 +4130,15 @@
       <c r="W44" t="inlineStr">
         <is>
           <t>@prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
-&lt;http://www.wikidata.org/entity/Q29644512&gt; &lt;http://www.wikidata.org/entity/P1454&gt; &lt;http://www.wikidata.org/entity/Q152074&gt; .
-&lt;http://www.wikidata.org/entity/Q152074&gt; &lt;http://www.wikidata.org/entity/P2348&gt; "2017" .
-&lt;http://www.wikidata.org/entity/Q29644512&gt; &lt;http://www.wikidata.org/entity/P136&gt; &lt;http://www.wikidata.org/entity/Q1358919&gt; .</t>
+&lt;http://www.wikidata.org/entity/Q29644512&gt; &lt;http://www.wikidata.org/entity/P527&gt; &lt;http://www.wikidata.org/entity/Q152074&gt; .
+&lt;http://www.wikidata.org/entity/Q29644512&gt; &lt;http://www.wikidata.org/entity/P710&gt; &lt;http://www.wikidata.org/entity/Q152074&gt; .
+&lt;http://www.wikidata.org/entity/Q29644512&gt; &lt;http://www.wikidata.org/entity/P127&gt; &lt;http://www.wikidata.org/entity/Q152074&gt; .
+&lt;http://www.wikidata.org/entity/Q29644512&gt; &lt;http://www.wikidata.org/entity/P361&gt; &lt;http://www.wikidata.org/entity/Q1358919&gt; .</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>b545f91d-d24b-45ef-a6e1-b0eb9e332b35</t>
         </is>
       </c>
     </row>
@@ -3980,77 +4147,83 @@
         <v>43</v>
       </c>
       <c r="B45" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C45" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D45" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E45" t="n">
         <v>9</v>
       </c>
       <c r="F45" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G45" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H45" t="n">
         <v>4</v>
       </c>
       <c r="I45" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J45" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K45" t="n">
         <v>7</v>
       </c>
       <c r="L45" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M45" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N45" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O45" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P45" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q45" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="R45" t="n">
         <v>9</v>
       </c>
       <c r="S45" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T45" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="U45" t="n">
         <v>10</v>
       </c>
       <c r="V45" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="W45" t="inlineStr">
         <is>
           <t>@prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
-wd:Q5288565 wd:P31 wd:Q7368 .
-wd:Q5288565 wd:P407 wd:Q1823 .
-wd:Q5288565 wd:P528 wd:Q7368 .
-wd:Q5288565 wd:P279 wd:Q651765 .
-wd:Q5288565 wd:P31 wd:Q7368 .
-wd:Q5288565 wd:P528 wd:Q7368 .</t>
+wd:Q5288565 wd:P279 wd:Q7368 .
+wd:Q7368 wd:P1535 wd:Q858177 .
+wd:Q42329 wd:P186 wd:Q197204 .
+wd:Q5288565 wd:P461 wd:Q142 .
+wd:Q7368 wd:P1056 wd:Q8495 .
+wd:Q5288565 wd:P366 wd:Q42329 .
+wd:Q5288565 wd:P495 wd:Q258 .</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>71c05695-66f7-4d09-9ad0-3377e8194797</t>
         </is>
       </c>
     </row>
@@ -4059,13 +4232,13 @@
         <v>44</v>
       </c>
       <c r="B46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E46" t="n">
         <v>3</v>
@@ -4089,19 +4262,19 @@
         <v>3</v>
       </c>
       <c r="L46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q46" t="n">
         <v>3</v>
@@ -4124,9 +4297,14 @@
       <c r="W46" t="inlineStr">
         <is>
           <t>@prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
-wd:Q92560 wd:P361 wd:Q231302 .
 wd:Q92560 wd:P287 wd:Q2061122 .
-wd:Q92560 wd:P449 wd:Q734663 .</t>
+wd:Q92560 wd:P449 wd:Q734663 .
+wd:Q92560 wd:P2360 wd:Q231302 .</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>ac47fab7-8246-40a0-87eb-40620329cc4b</t>
         </is>
       </c>
     </row>
@@ -4135,28 +4313,28 @@
         <v>45</v>
       </c>
       <c r="B47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E47" t="n">
         <v>3</v>
       </c>
       <c r="F47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H47" t="n">
         <v>2</v>
       </c>
       <c r="I47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J47" t="n">
         <v>2</v>
@@ -4165,43 +4343,49 @@
         <v>3</v>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R47" t="n">
         <v>3</v>
       </c>
       <c r="S47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T47" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U47" t="n">
         <v>4</v>
       </c>
       <c r="V47" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W47" t="inlineStr">
         <is>
           <t>@prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
 &lt;http://www.wikidata.org/entity/Q18036732&gt; &lt;http://www.wikidata.org/entity/P276&gt; &lt;http://www.wikidata.org/entity/Q753805&gt; .
-&lt;http://www.wikidata.org/entity/Q18036732&gt; &lt;http://www.wikidata.org/entity/P361&gt; &lt;http://www.wikidata.org/entity/Q7187&gt; .</t>
+&lt;http://www.wikidata.org/entity/Q18036732&gt; &lt;http://www.wikidata.org/entity/P279&gt; &lt;http://www.wikidata.org/entity/Q7187&gt; .
+&lt;http://www.wikidata.org/entity/Q753805&gt; &lt;http://www.wikidata.org/entity/P279&gt; &lt;http://www.wikidata.org/entity/Q186380&gt; .</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>c22a4591-4be1-4a65-ade1-52708dd8d895</t>
         </is>
       </c>
     </row>
@@ -4275,9 +4459,14 @@
       <c r="W48" t="inlineStr">
         <is>
           <t>@prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
-&lt;http://www.wikidata.org/entity/Q977911&gt; &lt;http://www.wikidata.org/entity/P131&gt; &lt;http://www.wikidata.org/entity/Q112686&gt; .
-&lt;http://www.wikidata.org/entity/Q977911&gt; &lt;http://www.wikidata.org/entity/P47&gt; &lt;http://www.wikidata.org/entity/Q979352&gt; .
-&lt;http://www.wikidata.org/entity/Q979352&gt; &lt;http://www.wikidata.org/entity/P131&gt; &lt;http://www.wikidata.org/entity/Q112686&gt; .</t>
+wd:Q977911 wd:P47 wd:Q979352 .
+wd:Q977911 wd:P131 wd:Q112686 .
+wd:Q979352 wd:P131 wd:Q112686 .</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>f1573dfd-e148-475c-8d94-16ecb9e42bbf</t>
         </is>
       </c>
     </row>
@@ -4286,22 +4475,22 @@
         <v>47</v>
       </c>
       <c r="B49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E49" t="n">
         <v>6</v>
       </c>
       <c r="F49" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G49" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H49" t="n">
         <v>2</v>
@@ -4316,19 +4505,19 @@
         <v>6</v>
       </c>
       <c r="L49" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M49" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N49" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O49" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P49" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q49" t="n">
         <v>5</v>
@@ -4337,25 +4526,30 @@
         <v>6</v>
       </c>
       <c r="S49" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T49" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U49" t="n">
         <v>7</v>
       </c>
       <c r="V49" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="W49" t="inlineStr">
         <is>
           <t>@prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
-&lt;http://www.wikidata.org/entity/Q311849&gt; &lt;http://www.wikidata.org/entity/P570&gt; [] .
-&lt;http://www.wikidata.org/entity/Q4546576&gt; &lt;http://www.wikidata.org/entity/P828&gt; &lt;http://www.wikidata.org/entity/Q173071&gt; .
-&lt;http://www.wikidata.org/entity/Q173071&gt; &lt;http://www.wikidata.org/entity/P156&gt; &lt;http://www.wikidata.org/entity/Q456854&gt; .
-&lt;http://www.wikidata.org/entity/Q4546576&gt; &lt;http://www.wikidata.org/entity/P541&gt; &lt;http://www.wikidata.org/entity/Q173071&gt;, &lt;http://www.wikidata.org/entity/Q170386&gt; .
-&lt;http://www.wikidata.org/entity/Q4546576&gt; &lt;http://www.wikidata.org/entity/P155&gt; &lt;http://www.wikidata.org/entity/Q311849&gt; .</t>
+wd:Q173071 wd:P991 wd:Q19546 .
+wd:Q4546576 wd:P541 wd:Q170386 .
+wd:Q4546576 wd:P156 wd:Q1358726 .
+wd:Q173071 wd:P361 wd:Q5 .
+wd:Q173071 wd:P1343 wd:Q602358 .</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>03213f3f-8877-4b08-bdf9-ffa2bd17cca2</t>
         </is>
       </c>
     </row>
@@ -4429,9 +4623,14 @@
       <c r="W50" t="inlineStr">
         <is>
           <t>@prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
-wd:Q2822458 wd:P131 wd:Q649 .
-wd:Q2822458 wd:P112 wd:Q4285526 .
-wd:Q2822458 wd:P361 wd:Q1140115 .</t>
+wd:Q2822458 wd:P361 wd:Q1140115 .
+wd:Q2822458 wd:P1535 wd:Q4285526 .
+wd:Q2822458 wd:P131 wd:Q649 .</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>b265d8b4-af34-4f40-9d62-f99f9afc0d7f</t>
         </is>
       </c>
     </row>
@@ -4440,13 +4639,13 @@
         <v>49</v>
       </c>
       <c r="B51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E51" t="n">
         <v>1</v>
@@ -4470,19 +4669,19 @@
         <v>1</v>
       </c>
       <c r="L51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
         <v>1</v>
@@ -4505,7 +4704,12 @@
       <c r="W51" t="inlineStr">
         <is>
           <t>@prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
-&lt;http://www.wikidata.org/entity/Q2362697&gt; &lt;http://www.wikidata.org/entity/P556&gt; &lt;http://www.wikidata.org/entity/Q503601&gt; .</t>
+&lt;http://www.wikidata.org/entity/Q2362697&gt; &lt;http://www.wikidata.org/entity/P361&gt; &lt;http://www.wikidata.org/entity/Q503601&gt; .</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>03ed4ed5-2b08-4311-a5f9-c67e070e99b9</t>
         </is>
       </c>
     </row>
